--- a/database/event/7902/event_7902_evp_summary.xlsx
+++ b/database/event/7902/event_7902_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.2081</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5.6215</v>
       </c>
       <c r="D2" t="n">
         <v>3.2985</v>
@@ -545,7 +545,7 @@
         <v>8.3423</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5.0929</v>
       </c>
       <c r="D3" t="n">
         <v>2.9487</v>
@@ -591,7 +591,7 @@
         <v>6.4022</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.9085</v>
       </c>
       <c r="D4" t="n">
         <v>2.165</v>
@@ -637,7 +637,7 @@
         <v>6.3886</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.9002</v>
       </c>
       <c r="D5" t="n">
         <v>2.1595</v>
@@ -683,7 +683,7 @@
         <v>5.5335</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3.3782</v>
       </c>
       <c r="D6" t="n">
         <v>1.814</v>
@@ -729,7 +729,7 @@
         <v>5.4147</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.3056</v>
       </c>
       <c r="D7" t="n">
         <v>1.7661</v>
@@ -775,7 +775,7 @@
         <v>5.3479</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3.2649</v>
       </c>
       <c r="D8" t="n">
         <v>1.7391</v>
@@ -821,7 +821,7 @@
         <v>4.8967</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.9894</v>
       </c>
       <c r="D9" t="n">
         <v>1.5568</v>
@@ -867,7 +867,7 @@
         <v>4.735</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.8907</v>
       </c>
       <c r="D10" t="n">
         <v>1.4915</v>
@@ -913,7 +913,7 @@
         <v>4.2118</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.5713</v>
       </c>
       <c r="D11" t="n">
         <v>1.2801</v>
@@ -959,7 +959,7 @@
         <v>4.1538</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.5359</v>
       </c>
       <c r="D12" t="n">
         <v>1.2567</v>
@@ -1005,7 +1005,7 @@
         <v>3.7774</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.3061</v>
       </c>
       <c r="D13" t="n">
         <v>1.1046</v>
@@ -1051,7 +1051,7 @@
         <v>3.4719</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.1196</v>
       </c>
       <c r="D14" t="n">
         <v>0.9812</v>
@@ -1097,7 +1097,7 @@
         <v>3.1146</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.9014</v>
       </c>
       <c r="D15" t="n">
         <v>0.8369</v>
@@ -1143,7 +1143,7 @@
         <v>2.9071</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.7748</v>
       </c>
       <c r="D16" t="n">
         <v>0.753</v>
@@ -1189,7 +1189,7 @@
         <v>2.8769</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.7563</v>
       </c>
       <c r="D17" t="n">
         <v>0.7408</v>
@@ -1235,7 +1235,7 @@
         <v>2.3542</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.4372</v>
       </c>
       <c r="D18" t="n">
         <v>0.5296999999999999</v>
@@ -1281,7 +1281,7 @@
         <v>2.244</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.3699</v>
       </c>
       <c r="D19" t="n">
         <v>0.4852</v>
@@ -1327,7 +1327,7 @@
         <v>2.0587</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.2568</v>
       </c>
       <c r="D20" t="n">
         <v>0.4103</v>
@@ -1373,7 +1373,7 @@
         <v>2.0275</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.2378</v>
       </c>
       <c r="D21" t="n">
         <v>0.3977</v>
@@ -1419,7 +1419,7 @@
         <v>1.801</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="D22" t="n">
         <v>0.3062</v>
@@ -1465,7 +1465,7 @@
         <v>1.7944</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.0955</v>
       </c>
       <c r="D23" t="n">
         <v>0.3035</v>
@@ -1511,7 +1511,7 @@
         <v>1.7758</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.0841</v>
       </c>
       <c r="D24" t="n">
         <v>0.296</v>
@@ -1557,7 +1557,7 @@
         <v>1.6617</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.0145</v>
       </c>
       <c r="D25" t="n">
         <v>0.2499</v>
@@ -1603,7 +1603,7 @@
         <v>1.6411</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.0019</v>
       </c>
       <c r="D26" t="n">
         <v>0.2416</v>
@@ -1649,7 +1649,7 @@
         <v>1.6045</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.9795</v>
       </c>
       <c r="D27" t="n">
         <v>0.2268</v>
@@ -1695,7 +1695,7 @@
         <v>1.5476</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.9448</v>
       </c>
       <c r="D28" t="n">
         <v>0.2038</v>
@@ -1741,7 +1741,7 @@
         <v>1.4994</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.9154</v>
       </c>
       <c r="D29" t="n">
         <v>0.1844</v>
@@ -1787,7 +1787,7 @@
         <v>1.4219</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.8681</v>
       </c>
       <c r="D30" t="n">
         <v>0.1531</v>
@@ -1833,7 +1833,7 @@
         <v>1.2859</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.785</v>
       </c>
       <c r="D31" t="n">
         <v>0.09810000000000001</v>
@@ -1879,7 +1879,7 @@
         <v>1.1672</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.7126</v>
       </c>
       <c r="D32" t="n">
         <v>0.0502</v>
@@ -1925,7 +1925,7 @@
         <v>1.1048</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
       <c r="D33" t="n">
         <v>0.025</v>
@@ -1971,7 +1971,7 @@
         <v>0.9408</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.5744</v>
       </c>
       <c r="D34" t="n">
         <v>-0.0413</v>
@@ -2017,7 +2017,7 @@
         <v>0.7719</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.4712</v>
       </c>
       <c r="D35" t="n">
         <v>-0.1095</v>
@@ -2063,7 +2063,7 @@
         <v>0.7037</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.4296</v>
       </c>
       <c r="D36" t="n">
         <v>-0.1371</v>
@@ -2109,7 +2109,7 @@
         <v>0.7030999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.4292</v>
       </c>
       <c r="D37" t="n">
         <v>-0.1373</v>
@@ -2155,7 +2155,7 @@
         <v>0.6716</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="D38" t="n">
         <v>-0.1501</v>
@@ -2201,7 +2201,7 @@
         <v>0.5837</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.3563</v>
       </c>
       <c r="D39" t="n">
         <v>-0.1856</v>
@@ -2247,7 +2247,7 @@
         <v>0.5407999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.3302</v>
       </c>
       <c r="D40" t="n">
         <v>-0.2029</v>
@@ -2293,7 +2293,7 @@
         <v>0.4518</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.2758</v>
       </c>
       <c r="D41" t="n">
         <v>-0.2388</v>
@@ -2339,7 +2339,7 @@
         <v>0.4408</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.2691</v>
       </c>
       <c r="D42" t="n">
         <v>-0.2433</v>
@@ -2385,7 +2385,7 @@
         <v>0.4088</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2496</v>
       </c>
       <c r="D43" t="n">
         <v>-0.2562</v>
@@ -2431,7 +2431,7 @@
         <v>0.3867</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.2361</v>
       </c>
       <c r="D44" t="n">
         <v>-0.2651</v>
@@ -2477,7 +2477,7 @@
         <v>0.382</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.2332</v>
       </c>
       <c r="D45" t="n">
         <v>-0.267</v>
@@ -2523,7 +2523,7 @@
         <v>0.347</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.2118</v>
       </c>
       <c r="D46" t="n">
         <v>-0.2812</v>
@@ -2569,7 +2569,7 @@
         <v>0.3164</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.1932</v>
       </c>
       <c r="D47" t="n">
         <v>-0.2935</v>
@@ -2615,7 +2615,7 @@
         <v>0.3129</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="D48" t="n">
         <v>-0.295</v>
@@ -2661,7 +2661,7 @@
         <v>0.2986</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1823</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3007</v>
@@ -2707,7 +2707,7 @@
         <v>0.2894</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1767</v>
       </c>
       <c r="D50" t="n">
         <v>-0.3045</v>
@@ -2753,7 +2753,7 @@
         <v>0.2375</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="D51" t="n">
         <v>-0.3254</v>
@@ -2799,7 +2799,7 @@
         <v>0.149</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="D52" t="n">
         <v>-0.3612</v>
@@ -2845,7 +2845,7 @@
         <v>0.1411</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.0861</v>
       </c>
       <c r="D53" t="n">
         <v>-0.3644</v>
@@ -2891,7 +2891,7 @@
         <v>0.119</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.0726</v>
       </c>
       <c r="D54" t="n">
         <v>-0.3733</v>
@@ -2937,7 +2937,7 @@
         <v>-0.0047</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.0029</v>
       </c>
       <c r="D55" t="n">
         <v>-0.4233</v>
@@ -2983,7 +2983,7 @@
         <v>-0.0618</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.0377</v>
       </c>
       <c r="D56" t="n">
         <v>-0.4463</v>
@@ -3029,7 +3029,7 @@
         <v>-0.0732</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.0447</v>
       </c>
       <c r="D57" t="n">
         <v>-0.4509</v>
@@ -3075,7 +3075,7 @@
         <v>-0.09569999999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.0584</v>
       </c>
       <c r="D58" t="n">
         <v>-0.46</v>
@@ -3121,7 +3121,7 @@
         <v>-0.228</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.1392</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5135</v>
@@ -3167,7 +3167,7 @@
         <v>-0.3824</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2335</v>
       </c>
       <c r="D60" t="n">
         <v>-0.5758</v>
@@ -3213,7 +3213,7 @@
         <v>-0.5864</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.358</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6583</v>
@@ -3259,7 +3259,7 @@
         <v>-0.6145</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.3751</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6696</v>
@@ -3305,7 +3305,7 @@
         <v>-0.6941000000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.4237</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7018</v>
@@ -3351,7 +3351,7 @@
         <v>-0.903</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.5513</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7862</v>
@@ -3397,7 +3397,7 @@
         <v>-0.9171</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.5599</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7919</v>
@@ -3443,7 +3443,7 @@
         <v>-0.9926</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.606</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8224</v>
@@ -3489,7 +3489,7 @@
         <v>-1.0047</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8272</v>
@@ -3535,7 +3535,7 @@
         <v>-1.0206</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.6231</v>
       </c>
       <c r="D68" t="n">
         <v>-0.8337</v>
@@ -3581,7 +3581,7 @@
         <v>-1.1695</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.714</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8938</v>
@@ -3627,7 +3627,7 @@
         <v>-1.1892</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.726</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9018</v>
@@ -3673,7 +3673,7 @@
         <v>-1.3392</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.8176</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9624</v>
@@ -3719,7 +3719,7 @@
         <v>-1.5443</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.9428</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0452</v>
@@ -3765,7 +3765,7 @@
         <v>-1.6048</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.9797</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0697</v>
@@ -3811,7 +3811,7 @@
         <v>-1.6847</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-1.0285</v>
       </c>
       <c r="D74" t="n">
         <v>-1.1019</v>
@@ -3857,7 +3857,7 @@
         <v>-1.818</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.1099</v>
       </c>
       <c r="D75" t="n">
         <v>-1.1558</v>
@@ -3903,7 +3903,7 @@
         <v>-1.8383</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.1223</v>
       </c>
       <c r="D76" t="n">
         <v>-1.164</v>
@@ -3949,7 +3949,7 @@
         <v>-1.9786</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.2079</v>
       </c>
       <c r="D77" t="n">
         <v>-1.2207</v>
@@ -3995,7 +3995,7 @@
         <v>-2.2746</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.3886</v>
       </c>
       <c r="D78" t="n">
         <v>-1.3403</v>
@@ -4041,7 +4041,7 @@
         <v>-2.6124</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.5949</v>
       </c>
       <c r="D79" t="n">
         <v>-1.4767</v>
@@ -4087,7 +4087,7 @@
         <v>-3.6106</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-2.2042</v>
       </c>
       <c r="D80" t="n">
         <v>-1.88</v>
@@ -4133,7 +4133,7 @@
         <v>-3.9667</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.4216</v>
       </c>
       <c r="D81" t="n">
         <v>-2.0238</v>

--- a/database/event/7902/event_7902_evp_summary.xlsx
+++ b/database/event/7902/event_7902_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.2081</v>
+        <v>10.2558</v>
       </c>
       <c r="C2" t="n">
-        <v>5.6215</v>
+        <v>6.2611</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2985</v>
+        <v>3.642</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2081</v>
+        <v>10.2558</v>
       </c>
       <c r="F2" t="n">
-        <v>3.294</v>
+        <v>4.3416</v>
       </c>
       <c r="G2" t="n">
         <v>5.9142</v>
       </c>
       <c r="H2" t="n">
-        <v>3.294</v>
+        <v>4.5046</v>
       </c>
       <c r="I2" t="n">
-        <v>3.294</v>
+        <v>4.5046</v>
       </c>
       <c r="J2" t="n">
         <v>5.9142</v>
@@ -529,7 +529,7 @@
         <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>9.2082</v>
+        <v>10.4188</v>
       </c>
       <c r="N2" t="n">
         <v>245</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.3423</v>
+        <v>8.7432</v>
       </c>
       <c r="C3" t="n">
-        <v>5.0929</v>
+        <v>5.3377</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9487</v>
+        <v>3.0394</v>
       </c>
       <c r="E3" t="n">
-        <v>8.3423</v>
+        <v>8.7432</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0356</v>
+        <v>4.4365</v>
       </c>
       <c r="G3" t="n">
         <v>4.3067</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0356</v>
+        <v>4.6534</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0356</v>
+        <v>4.6534</v>
       </c>
       <c r="J3" t="n">
         <v>4.3067</v>
@@ -575,7 +575,7 @@
         <v>136</v>
       </c>
       <c r="M3" t="n">
-        <v>8.3423</v>
+        <v>8.960100000000001</v>
       </c>
       <c r="N3" t="n">
         <v>313</v>
@@ -584,47 +584,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4022</v>
+        <v>6.4167</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9085</v>
+        <v>3.9174</v>
       </c>
       <c r="D4" t="n">
-        <v>2.165</v>
+        <v>2.1125</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4022</v>
+        <v>6.4167</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2281</v>
+        <v>4.4327</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1741</v>
+        <v>1.984</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3266</v>
+        <v>4.6475</v>
       </c>
       <c r="I4" t="n">
-        <v>4.367</v>
+        <v>4.6475</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1741</v>
+        <v>1.984</v>
       </c>
       <c r="K4" t="n">
-        <v>256</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5411</v>
+        <v>6.6315</v>
       </c>
       <c r="N4" t="n">
-        <v>404</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5">
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3886</v>
+        <v>6.3846</v>
       </c>
       <c r="C5" t="n">
-        <v>3.9002</v>
+        <v>3.8978</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1595</v>
+        <v>2.0997</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3886</v>
+        <v>6.3846</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2052</v>
+        <v>4.2012</v>
       </c>
       <c r="G5" t="n">
         <v>2.1834</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2907</v>
+        <v>4.2844</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3307</v>
+        <v>4.3568</v>
       </c>
       <c r="J5" t="n">
         <v>2.1834</v>
@@ -667,7 +667,7 @@
         <v>104</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5141</v>
+        <v>6.5402</v>
       </c>
       <c r="N5" t="n">
         <v>315</v>
@@ -676,219 +676,219 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.5335</v>
+        <v>6.3817</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3782</v>
+        <v>3.896</v>
       </c>
       <c r="D6" t="n">
-        <v>1.814</v>
+        <v>2.0986</v>
       </c>
       <c r="E6" t="n">
-        <v>5.5335</v>
+        <v>6.3817</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8363</v>
+        <v>4.2076</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6972</v>
+        <v>2.1741</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8363</v>
+        <v>4.2944</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8363</v>
+        <v>4.367</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6972</v>
+        <v>2.1741</v>
       </c>
       <c r="K6" t="n">
-        <v>177</v>
+        <v>256</v>
       </c>
       <c r="L6" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="M6" t="n">
-        <v>5.5335</v>
+        <v>6.5411</v>
       </c>
       <c r="N6" t="n">
-        <v>313</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.4147</v>
+        <v>5.7692</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3056</v>
+        <v>3.5221</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7661</v>
+        <v>1.8545</v>
       </c>
       <c r="E7" t="n">
-        <v>5.4147</v>
+        <v>5.7692</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4307</v>
+        <v>2.072</v>
       </c>
       <c r="G7" t="n">
-        <v>1.984</v>
+        <v>3.6972</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4307</v>
+        <v>2.072</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4307</v>
+        <v>2.072</v>
       </c>
       <c r="J7" t="n">
-        <v>1.984</v>
+        <v>3.6972</v>
       </c>
       <c r="K7" t="n">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="L7" t="n">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="M7" t="n">
-        <v>5.4147</v>
+        <v>5.7692</v>
       </c>
       <c r="N7" t="n">
-        <v>167</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.3479</v>
+        <v>5.6269</v>
       </c>
       <c r="C8" t="n">
-        <v>3.2649</v>
+        <v>3.4352</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7391</v>
+        <v>1.7978</v>
       </c>
       <c r="E8" t="n">
-        <v>5.3479</v>
+        <v>5.6269</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4173</v>
+        <v>3.6957</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9306</v>
+        <v>1.9312</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4173</v>
+        <v>3.6957</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4492</v>
+        <v>3.6957</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9306</v>
+        <v>1.9312</v>
       </c>
       <c r="K8" t="n">
-        <v>256</v>
+        <v>88</v>
       </c>
       <c r="L8" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M8" t="n">
-        <v>5.379799999999999</v>
+        <v>5.6269</v>
       </c>
       <c r="N8" t="n">
-        <v>404</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.8967</v>
+        <v>5.3225</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9894</v>
+        <v>3.2494</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5568</v>
+        <v>1.6766</v>
       </c>
       <c r="E9" t="n">
-        <v>4.8967</v>
+        <v>5.3225</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5459000000000001</v>
+        <v>3.3919</v>
       </c>
       <c r="G9" t="n">
-        <v>4.3508</v>
+        <v>1.9306</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5459000000000001</v>
+        <v>3.3919</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5459000000000001</v>
+        <v>3.4492</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3508</v>
+        <v>1.9306</v>
       </c>
       <c r="K9" t="n">
-        <v>88</v>
+        <v>256</v>
       </c>
       <c r="L9" t="n">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="M9" t="n">
-        <v>4.896699999999999</v>
+        <v>5.379799999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>245</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.735</v>
+        <v>4.899</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8907</v>
+        <v>2.9908</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4915</v>
+        <v>1.5079</v>
       </c>
       <c r="E10" t="n">
-        <v>4.735</v>
+        <v>4.899</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8038</v>
+        <v>0.5482</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9312</v>
+        <v>4.3508</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8038</v>
+        <v>0.5482</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8038</v>
+        <v>0.5482</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9312</v>
+        <v>4.3508</v>
       </c>
       <c r="K10" t="n">
         <v>88</v>
@@ -897,7 +897,7 @@
         <v>157</v>
       </c>
       <c r="M10" t="n">
-        <v>4.734999999999999</v>
+        <v>4.898999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>245</v>
@@ -906,170 +906,170 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.2118</v>
+        <v>4.2475</v>
       </c>
       <c r="C11" t="n">
-        <v>2.5713</v>
+        <v>2.5931</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2801</v>
+        <v>1.2483</v>
       </c>
       <c r="E11" t="n">
-        <v>4.2118</v>
+        <v>4.2475</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4185</v>
+        <v>2.8984</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7933</v>
+        <v>1.3491</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4185</v>
+        <v>2.8984</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4185</v>
+        <v>2.8984</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7933</v>
+        <v>1.3491</v>
       </c>
       <c r="K11" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="L11" t="n">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2118</v>
+        <v>4.2475</v>
       </c>
       <c r="N11" t="n">
-        <v>245</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.1538</v>
+        <v>4.2141</v>
       </c>
       <c r="C12" t="n">
-        <v>2.5359</v>
+        <v>2.5727</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2567</v>
+        <v>1.235</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1538</v>
+        <v>4.2141</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8047</v>
+        <v>1.4208</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3491</v>
+        <v>2.7933</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8047</v>
+        <v>1.4208</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8047</v>
+        <v>1.4208</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3491</v>
+        <v>2.7933</v>
       </c>
       <c r="K12" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="L12" t="n">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1538</v>
+        <v>4.2141</v>
       </c>
       <c r="N12" t="n">
-        <v>146</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.7774</v>
+        <v>3.9366</v>
       </c>
       <c r="C13" t="n">
-        <v>2.3061</v>
+        <v>2.4033</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1046</v>
+        <v>1.1244</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7774</v>
+        <v>3.9366</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7774</v>
+        <v>4.2975</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.3609</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7774</v>
+        <v>4.4355</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7774</v>
+        <v>4.4355</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.3609</v>
       </c>
       <c r="K13" t="n">
-        <v>174</v>
+        <v>103</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7774</v>
+        <v>4.0746</v>
       </c>
       <c r="N13" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.4719</v>
+        <v>3.9306</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1196</v>
+        <v>2.3996</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9812</v>
+        <v>1.122</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4719</v>
+        <v>3.9306</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4719</v>
+        <v>3.9306</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4719</v>
+        <v>3.9306</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4719</v>
+        <v>3.9306</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4719</v>
+        <v>3.9306</v>
       </c>
       <c r="N14" t="n">
         <v>174</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.1146</v>
+        <v>3.896</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9014</v>
+        <v>2.3785</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8369</v>
+        <v>1.1083</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1146</v>
+        <v>3.896</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4755</v>
+        <v>3.896</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3609</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4755</v>
+        <v>3.896</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4755</v>
+        <v>3.896</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3609</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="L15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1146</v>
+        <v>3.896</v>
       </c>
       <c r="N15" t="n">
-        <v>149</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9071</v>
+        <v>3.2181</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7748</v>
+        <v>1.9646</v>
       </c>
       <c r="D16" t="n">
-        <v>0.753</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9071</v>
+        <v>3.2181</v>
       </c>
       <c r="F16" t="n">
-        <v>2.252</v>
+        <v>2.563</v>
       </c>
       <c r="G16" t="n">
         <v>0.6551</v>
       </c>
       <c r="H16" t="n">
-        <v>2.252</v>
+        <v>2.563</v>
       </c>
       <c r="I16" t="n">
-        <v>2.252</v>
+        <v>2.563</v>
       </c>
       <c r="J16" t="n">
         <v>0.6551</v>
@@ -1173,7 +1173,7 @@
         <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9071</v>
+        <v>3.2181</v>
       </c>
       <c r="N16" t="n">
         <v>216</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8769</v>
+        <v>3.144</v>
       </c>
       <c r="C17" t="n">
-        <v>1.7563</v>
+        <v>1.9194</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7408</v>
+        <v>0.8087</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8769</v>
+        <v>3.144</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8755</v>
+        <v>3.1426</v>
       </c>
       <c r="G17" t="n">
         <v>0.0014</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8755</v>
+        <v>3.1426</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8755</v>
+        <v>3.1426</v>
       </c>
       <c r="J17" t="n">
         <v>0.0014</v>
@@ -1219,7 +1219,7 @@
         <v>68</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8769</v>
+        <v>3.144</v>
       </c>
       <c r="N17" t="n">
         <v>146</v>
@@ -1228,630 +1228,630 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3542</v>
+        <v>2.9994</v>
       </c>
       <c r="C18" t="n">
-        <v>1.4372</v>
+        <v>1.8311</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.7511</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3542</v>
+        <v>2.9994</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0946</v>
+        <v>2.9994</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2596</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0946</v>
+        <v>2.9994</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1142</v>
+        <v>2.9994</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2596</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L18" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3738</v>
+        <v>2.9994</v>
       </c>
       <c r="N18" t="n">
-        <v>315</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.244</v>
+        <v>2.3386</v>
       </c>
       <c r="C19" t="n">
-        <v>1.3699</v>
+        <v>1.4277</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4852</v>
+        <v>0.4878</v>
       </c>
       <c r="E19" t="n">
-        <v>2.244</v>
+        <v>2.3386</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6784</v>
+        <v>2.079</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5656</v>
+        <v>0.2596</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6784</v>
+        <v>2.079</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6847</v>
+        <v>2.1142</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5656</v>
+        <v>0.2596</v>
       </c>
       <c r="K19" t="n">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="L19" t="n">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2503</v>
+        <v>2.3738</v>
       </c>
       <c r="N19" t="n">
-        <v>404</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0587</v>
+        <v>2.2389</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2568</v>
+        <v>1.3668</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4103</v>
+        <v>0.4481</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0587</v>
+        <v>2.2389</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0587</v>
+        <v>0.6733</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.5656</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0587</v>
+        <v>0.6733</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0587</v>
+        <v>0.6847</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.5656</v>
       </c>
       <c r="K20" t="n">
-        <v>174</v>
+        <v>256</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0587</v>
+        <v>2.2503</v>
       </c>
       <c r="N20" t="n">
-        <v>174</v>
+        <v>404</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0275</v>
+        <v>2.1178</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2378</v>
+        <v>1.2929</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3977</v>
+        <v>0.3998</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0275</v>
+        <v>2.1178</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0275</v>
+        <v>2.1989</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0275</v>
+        <v>2.1989</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0275</v>
+        <v>2.1989</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0275</v>
+        <v>2.1178</v>
       </c>
       <c r="N21" t="n">
-        <v>206</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.801</v>
+        <v>2.098</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0995</v>
+        <v>1.2808</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3062</v>
+        <v>0.3919</v>
       </c>
       <c r="E22" t="n">
-        <v>1.801</v>
+        <v>2.098</v>
       </c>
       <c r="F22" t="n">
-        <v>1.801</v>
+        <v>2.6515</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.5535</v>
       </c>
       <c r="H22" t="n">
-        <v>1.801</v>
+        <v>2.6515</v>
       </c>
       <c r="I22" t="n">
-        <v>1.801</v>
+        <v>2.6515</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.5535</v>
       </c>
       <c r="K22" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M22" t="n">
-        <v>1.801</v>
+        <v>2.098</v>
       </c>
       <c r="N22" t="n">
-        <v>184</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7944</v>
+        <v>2.077</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0955</v>
+        <v>1.268</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3035</v>
+        <v>0.3836</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7944</v>
+        <v>2.077</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9898</v>
+        <v>2.077</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1954</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9898</v>
+        <v>2.077</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0083</v>
+        <v>2.077</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1954</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="L23" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8129</v>
+        <v>2.077</v>
       </c>
       <c r="N23" t="n">
-        <v>315</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7758</v>
+        <v>2.0587</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0841</v>
+        <v>1.2568</v>
       </c>
       <c r="D24" t="n">
-        <v>0.296</v>
+        <v>0.3763</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7758</v>
+        <v>2.0587</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8569</v>
+        <v>2.0587</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.08110000000000001</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8569</v>
+        <v>2.0587</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8569</v>
+        <v>2.0587</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.08110000000000001</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="L24" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7758</v>
+        <v>2.0587</v>
       </c>
       <c r="N24" t="n">
-        <v>149</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6617</v>
+        <v>2.0349</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0145</v>
+        <v>1.2423</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2499</v>
+        <v>0.3668</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6617</v>
+        <v>2.0349</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8841</v>
+        <v>2.9761</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2224</v>
+        <v>-0.9412</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8841</v>
+        <v>2.9761</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8841</v>
+        <v>2.9761</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2224</v>
+        <v>-0.9412</v>
       </c>
       <c r="K25" t="n">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="L25" t="n">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6617</v>
+        <v>2.0349</v>
       </c>
       <c r="N25" t="n">
-        <v>216</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6411</v>
+        <v>1.9481</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0019</v>
+        <v>1.1893</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2416</v>
+        <v>0.3322</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6411</v>
+        <v>1.9481</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6239</v>
+        <v>2.3409</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0172</v>
+        <v>-0.3928</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6239</v>
+        <v>2.3409</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6239</v>
+        <v>2.3409</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0172</v>
+        <v>-0.3928</v>
       </c>
       <c r="K26" t="n">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="L26" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6411</v>
+        <v>1.9481</v>
       </c>
       <c r="N26" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6045</v>
+        <v>1.7827</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9795</v>
+        <v>1.0883</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2268</v>
+        <v>0.2663</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6045</v>
+        <v>1.7827</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6045</v>
+        <v>2.007</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.2243</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6045</v>
+        <v>2.007</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6045</v>
+        <v>2.007</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.2243</v>
       </c>
       <c r="K27" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6045</v>
+        <v>1.7827</v>
       </c>
       <c r="N27" t="n">
-        <v>117</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5476</v>
+        <v>1.7796</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9448</v>
+        <v>1.0864</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2038</v>
+        <v>0.2651</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5476</v>
+        <v>1.7796</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5476</v>
+        <v>1.975</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.1954</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5476</v>
+        <v>1.975</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5476</v>
+        <v>2.0083</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.1954</v>
       </c>
       <c r="K28" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5476</v>
+        <v>1.8129</v>
       </c>
       <c r="N28" t="n">
-        <v>206</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4994</v>
+        <v>1.6877</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9154</v>
+        <v>1.0303</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1844</v>
+        <v>0.2285</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4994</v>
+        <v>1.6877</v>
       </c>
       <c r="F29" t="n">
-        <v>1.7237</v>
+        <v>1.9101</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2243</v>
+        <v>-0.2224</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7237</v>
+        <v>1.9101</v>
       </c>
       <c r="I29" t="n">
-        <v>1.7237</v>
+        <v>1.9101</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2243</v>
+        <v>-0.2224</v>
       </c>
       <c r="K29" t="n">
-        <v>76</v>
+        <v>170</v>
       </c>
       <c r="L29" t="n">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4994</v>
+        <v>1.6877</v>
       </c>
       <c r="N29" t="n">
-        <v>167</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4219</v>
+        <v>1.6411</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8681</v>
+        <v>1.0019</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1531</v>
+        <v>0.2099</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4219</v>
+        <v>1.6411</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4085</v>
+        <v>1.6239</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0134</v>
+        <v>0.0172</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4085</v>
+        <v>1.6239</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4085</v>
+        <v>1.6239</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0134</v>
+        <v>0.0172</v>
       </c>
       <c r="K30" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="L30" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4219</v>
+        <v>1.6411</v>
       </c>
       <c r="N30" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2859</v>
+        <v>1.6222</v>
       </c>
       <c r="C31" t="n">
-        <v>0.785</v>
+        <v>0.9903</v>
       </c>
       <c r="D31" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.2024</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2859</v>
+        <v>1.6222</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2859</v>
+        <v>1.6222</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2859</v>
+        <v>1.6222</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2859</v>
+        <v>1.6222</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2859</v>
+        <v>1.6222</v>
       </c>
       <c r="N31" t="n">
         <v>206</v>
@@ -1872,173 +1872,173 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1672</v>
+        <v>1.6045</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7126</v>
+        <v>0.9795</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0502</v>
+        <v>0.1953</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1672</v>
+        <v>1.6045</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7207</v>
+        <v>1.6045</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5535</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7207</v>
+        <v>1.6045</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7207</v>
+        <v>1.6045</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5535</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="L32" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1672</v>
+        <v>1.6045</v>
       </c>
       <c r="N32" t="n">
-        <v>216</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1048</v>
+        <v>1.5974</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6745</v>
+        <v>0.9752</v>
       </c>
       <c r="D33" t="n">
-        <v>0.025</v>
+        <v>0.1925</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1048</v>
+        <v>1.5974</v>
       </c>
       <c r="F33" t="n">
-        <v>2.046</v>
+        <v>1.5974</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.9412</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.046</v>
+        <v>1.5974</v>
       </c>
       <c r="I33" t="n">
-        <v>2.046</v>
+        <v>1.5974</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9412</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>76</v>
+        <v>206</v>
       </c>
       <c r="L33" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1048</v>
+        <v>1.5974</v>
       </c>
       <c r="N33" t="n">
-        <v>167</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9408</v>
+        <v>1.5367</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5744</v>
+        <v>0.9381</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0413</v>
+        <v>0.1683</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9408</v>
+        <v>1.5367</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8316</v>
+        <v>1.5367</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1092</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8316</v>
+        <v>1.5367</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8316</v>
+        <v>1.5367</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1092</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L34" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9408</v>
+        <v>1.5367</v>
       </c>
       <c r="N34" t="n">
-        <v>149</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7719</v>
+        <v>1.4219</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4712</v>
+        <v>0.8681</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1095</v>
+        <v>0.1226</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7719</v>
+        <v>1.4219</v>
       </c>
       <c r="F35" t="n">
-        <v>1.1647</v>
+        <v>1.4085</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.3928</v>
+        <v>0.0134</v>
       </c>
       <c r="H35" t="n">
-        <v>1.1647</v>
+        <v>1.4085</v>
       </c>
       <c r="I35" t="n">
-        <v>1.1647</v>
+        <v>1.4085</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3928</v>
+        <v>0.0134</v>
       </c>
       <c r="K35" t="n">
         <v>78</v>
@@ -2047,7 +2047,7 @@
         <v>68</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7719</v>
+        <v>1.4219</v>
       </c>
       <c r="N35" t="n">
         <v>146</v>
@@ -2056,1243 +2056,1243 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7037</v>
+        <v>1.0797</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4296</v>
+        <v>0.6592</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1371</v>
+        <v>-0.0138</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7037</v>
+        <v>1.0797</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7037</v>
+        <v>1.0797</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7037</v>
+        <v>1.0797</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7037</v>
+        <v>1.0797</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7037</v>
+        <v>1.0797</v>
       </c>
       <c r="N36" t="n">
-        <v>174</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.9426</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4292</v>
+        <v>0.5755</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1373</v>
+        <v>-0.0684</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.9426</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.8334</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.1092</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.8334</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.8334</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.1092</v>
       </c>
       <c r="K37" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.9426</v>
       </c>
       <c r="N37" t="n">
-        <v>107</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6716</v>
+        <v>0.9386</v>
       </c>
       <c r="C38" t="n">
-        <v>0.41</v>
+        <v>0.573</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1501</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6716</v>
+        <v>0.9386</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6716</v>
+        <v>0.176</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6716</v>
+        <v>0.176</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6716</v>
+        <v>0.176</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6716</v>
+        <v>0.9385999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>113</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>z4kr</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5837</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3563</v>
+        <v>0.4705</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1856</v>
+        <v>-0.1369</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5837</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.1789</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7625999999999999</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.1789</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1789</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7625999999999999</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="L39" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5836999999999999</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>245</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.7045</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3302</v>
+        <v>0.4301</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2029</v>
+        <v>-0.1632</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.7045</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1113</v>
+        <v>0.7045</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4295</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1113</v>
+        <v>0.7045</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1113</v>
+        <v>0.7045</v>
       </c>
       <c r="J40" t="n">
-        <v>0.4295</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="L40" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.7045</v>
       </c>
       <c r="N40" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4518</v>
+        <v>0.6456</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2758</v>
+        <v>0.3941</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2388</v>
+        <v>-0.1867</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4518</v>
+        <v>0.6456</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3733</v>
+        <v>0.6456</v>
       </c>
       <c r="G41" t="n">
-        <v>1.8251</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3733</v>
+        <v>0.6456</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3733</v>
+        <v>0.6456</v>
       </c>
       <c r="J41" t="n">
-        <v>1.8251</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="L41" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4518</v>
+        <v>0.6456</v>
       </c>
       <c r="N41" t="n">
-        <v>313</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4408</v>
+        <v>0.6106</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2691</v>
+        <v>0.3728</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2433</v>
+        <v>-0.2006</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4408</v>
+        <v>0.6106</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.6106</v>
       </c>
       <c r="G42" t="n">
-        <v>0.536</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.6106</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.6106</v>
       </c>
       <c r="J42" t="n">
-        <v>0.536</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="L42" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4408</v>
+        <v>0.6106</v>
       </c>
       <c r="N42" t="n">
-        <v>216</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>riskyb0b</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4088</v>
+        <v>0.5907</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2496</v>
+        <v>0.3606</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2562</v>
+        <v>-0.2086</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4088</v>
+        <v>0.5907</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4088</v>
+        <v>0.0547</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.536</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4088</v>
+        <v>0.0547</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4088</v>
+        <v>0.0547</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.536</v>
       </c>
       <c r="K43" t="n">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4088</v>
+        <v>0.5907</v>
       </c>
       <c r="N43" t="n">
-        <v>101</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3867</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2361</v>
+        <v>0.3302</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2651</v>
+        <v>-0.2285</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3867</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3088</v>
+        <v>0.1113</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0779</v>
+        <v>0.4295</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3088</v>
+        <v>0.1113</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3088</v>
+        <v>0.1113</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0779</v>
+        <v>0.4295</v>
       </c>
       <c r="K44" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L44" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3867</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>146</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.382</v>
+        <v>0.5081</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2332</v>
+        <v>0.3102</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.267</v>
+        <v>-0.2415</v>
       </c>
       <c r="E45" t="n">
-        <v>0.382</v>
+        <v>0.5081</v>
       </c>
       <c r="F45" t="n">
-        <v>0.382</v>
+        <v>1.7229</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-1.2148</v>
       </c>
       <c r="H45" t="n">
-        <v>0.382</v>
+        <v>1.7229</v>
       </c>
       <c r="I45" t="n">
-        <v>0.382</v>
+        <v>1.7229</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-1.2148</v>
       </c>
       <c r="K45" t="n">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M45" t="n">
-        <v>0.382</v>
+        <v>0.5081</v>
       </c>
       <c r="N45" t="n">
-        <v>117</v>
+        <v>313</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.347</v>
+        <v>0.4541</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2118</v>
+        <v>0.2772</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2812</v>
+        <v>-0.263</v>
       </c>
       <c r="E46" t="n">
-        <v>0.347</v>
+        <v>0.4541</v>
       </c>
       <c r="F46" t="n">
-        <v>0.347</v>
+        <v>0.4541</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.347</v>
+        <v>0.4541</v>
       </c>
       <c r="I46" t="n">
-        <v>0.347</v>
+        <v>0.4541</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.347</v>
+        <v>0.4541</v>
       </c>
       <c r="N46" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3164</v>
+        <v>0.4518</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1932</v>
+        <v>0.2758</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2935</v>
+        <v>-0.2639</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3164</v>
+        <v>0.4518</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3164</v>
+        <v>-1.3733</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1.8251</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3164</v>
+        <v>-1.3733</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3164</v>
+        <v>-1.3733</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1.8251</v>
       </c>
       <c r="K47" t="n">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M47" t="n">
-        <v>0.3164</v>
+        <v>0.4518</v>
       </c>
       <c r="N47" t="n">
-        <v>184</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>riskyb0b</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3129</v>
+        <v>0.4088</v>
       </c>
       <c r="C48" t="n">
-        <v>0.191</v>
+        <v>0.2496</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.295</v>
+        <v>-0.281</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3129</v>
+        <v>0.4088</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3129</v>
+        <v>0.4088</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3129</v>
+        <v>0.4088</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3129</v>
+        <v>0.4088</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3129</v>
+        <v>0.4088</v>
       </c>
       <c r="N48" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.2986</v>
+        <v>0.3867</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1823</v>
+        <v>0.2361</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3007</v>
+        <v>-0.2898</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2986</v>
+        <v>0.3867</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2986</v>
+        <v>0.3088</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.0779</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2986</v>
+        <v>0.3088</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2986</v>
+        <v>0.3088</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.0779</v>
       </c>
       <c r="K49" t="n">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2986</v>
+        <v>0.3867</v>
       </c>
       <c r="N49" t="n">
-        <v>206</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Xant3r</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.2894</v>
+        <v>0.382</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1767</v>
+        <v>0.2332</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3045</v>
+        <v>-0.2917</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2894</v>
+        <v>0.382</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2894</v>
+        <v>0.382</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2894</v>
+        <v>0.382</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2894</v>
+        <v>0.382</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.2894</v>
+        <v>0.382</v>
       </c>
       <c r="N50" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.2375</v>
+        <v>0.347</v>
       </c>
       <c r="C51" t="n">
-        <v>0.145</v>
+        <v>0.2118</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3254</v>
+        <v>-0.3057</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2375</v>
+        <v>0.347</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2375</v>
+        <v>0.347</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2375</v>
+        <v>0.347</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2375</v>
+        <v>0.347</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2375</v>
+        <v>0.347</v>
       </c>
       <c r="N51" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Xant3r</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.149</v>
+        <v>0.3183</v>
       </c>
       <c r="C52" t="n">
-        <v>0.091</v>
+        <v>0.1943</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3612</v>
+        <v>-0.3171</v>
       </c>
       <c r="E52" t="n">
-        <v>0.149</v>
+        <v>0.3183</v>
       </c>
       <c r="F52" t="n">
-        <v>0.149</v>
+        <v>0.3183</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.149</v>
+        <v>0.3183</v>
       </c>
       <c r="I52" t="n">
-        <v>0.149</v>
+        <v>0.3183</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.149</v>
+        <v>0.3183</v>
       </c>
       <c r="N52" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.1411</v>
+        <v>0.3171</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0861</v>
+        <v>0.1936</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3644</v>
+        <v>-0.3176</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1411</v>
+        <v>0.3171</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.404</v>
+        <v>0.3171</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5451</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.404</v>
+        <v>0.3171</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.404</v>
+        <v>0.3171</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5451</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="L53" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1411</v>
+        <v>0.3171</v>
       </c>
       <c r="N53" t="n">
-        <v>313</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>khaN</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.119</v>
+        <v>0.3129</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0726</v>
+        <v>0.191</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3733</v>
+        <v>-0.3193</v>
       </c>
       <c r="E54" t="n">
-        <v>0.119</v>
+        <v>0.3129</v>
       </c>
       <c r="F54" t="n">
-        <v>0.119</v>
+        <v>0.3129</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.119</v>
+        <v>0.3129</v>
       </c>
       <c r="I54" t="n">
-        <v>0.119</v>
+        <v>0.3129</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.119</v>
+        <v>0.3129</v>
       </c>
       <c r="N54" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0047</v>
+        <v>0.187</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0029</v>
+        <v>0.1142</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4233</v>
+        <v>-0.3694</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0047</v>
+        <v>0.187</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0047</v>
+        <v>0.187</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0047</v>
+        <v>0.187</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0047</v>
+        <v>0.187</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.0047</v>
+        <v>0.187</v>
       </c>
       <c r="N55" t="n">
-        <v>113</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0618</v>
+        <v>0.1411</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0377</v>
+        <v>0.0861</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4463</v>
+        <v>-0.3877</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0618</v>
+        <v>0.1411</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0618</v>
+        <v>-0.404</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.5451</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0618</v>
+        <v>-0.404</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0618</v>
+        <v>-0.404</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>0.5451</v>
       </c>
       <c r="K56" t="n">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.0618</v>
+        <v>0.1411</v>
       </c>
       <c r="N56" t="n">
-        <v>121</v>
+        <v>313</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>khaN</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.0732</v>
+        <v>0.119</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0447</v>
+        <v>0.0726</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4509</v>
+        <v>-0.3965</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0732</v>
+        <v>0.119</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9187</v>
+        <v>0.119</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9187</v>
+        <v>0.119</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9273</v>
+        <v>0.119</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>211</v>
+        <v>101</v>
       </c>
       <c r="L57" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.06459999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="N57" t="n">
-        <v>315</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0047</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0584</v>
+        <v>-0.0029</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.46</v>
+        <v>-0.4458</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0047</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0047</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0047</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0047</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0047</v>
       </c>
       <c r="N58" t="n">
-        <v>174</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.228</v>
+        <v>-0.0618</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1392</v>
+        <v>-0.0377</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5135</v>
+        <v>-0.4685</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.228</v>
+        <v>-0.0618</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.228</v>
+        <v>-0.0618</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.228</v>
+        <v>-0.0618</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.228</v>
+        <v>-0.0618</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.228</v>
+        <v>-0.0618</v>
       </c>
       <c r="N59" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3824</v>
+        <v>-0.08</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2335</v>
+        <v>-0.0488</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5758</v>
+        <v>-0.4758</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3824</v>
+        <v>-0.08</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8324</v>
+        <v>0.9119</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.2148</v>
+        <v>-0.9919</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8324</v>
+        <v>0.9119</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8324</v>
+        <v>0.9273</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.2148</v>
+        <v>-0.9919</v>
       </c>
       <c r="K60" t="n">
-        <v>177</v>
+        <v>211</v>
       </c>
       <c r="L60" t="n">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.3824000000000001</v>
+        <v>-0.06459999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5864</v>
+        <v>-0.1522</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.358</v>
+        <v>-0.0929</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6583</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5864</v>
+        <v>-0.1522</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5864</v>
+        <v>-0.1522</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5864</v>
+        <v>-0.1522</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5864</v>
+        <v>-0.1522</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5864</v>
+        <v>-0.1522</v>
       </c>
       <c r="N61" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6145</v>
+        <v>-0.1571</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3751</v>
+        <v>-0.0959</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6696</v>
+        <v>-0.5065</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6145</v>
+        <v>-0.1571</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6145</v>
+        <v>-0.1571</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6145</v>
+        <v>-0.1571</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.6145</v>
+        <v>-0.1571</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>121</v>
+        <v>206</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.6145</v>
+        <v>-0.1571</v>
       </c>
       <c r="N62" t="n">
-        <v>121</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63">
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.3188</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4237</v>
+        <v>-0.1946</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7018</v>
+        <v>-0.5709</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.3188</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.3188</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.3188</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.3188</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.3188</v>
       </c>
       <c r="N63" t="n">
         <v>121</v>
@@ -3344,47 +3344,47 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.903</v>
+        <v>-0.5864</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.5513</v>
+        <v>-0.358</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7862</v>
+        <v>-0.6775</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.903</v>
+        <v>-0.5864</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.903</v>
+        <v>-0.5864</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.903</v>
+        <v>-0.5864</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.903</v>
+        <v>-0.5864</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>206</v>
+        <v>117</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.903</v>
+        <v>-0.5864</v>
       </c>
       <c r="N64" t="n">
-        <v>206</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65">
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.9171</v>
+        <v>-0.6513</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.5599</v>
+        <v>-0.3976</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7919</v>
+        <v>-0.7034</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.9171</v>
+        <v>-0.6513</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.9171</v>
+        <v>-0.6513</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.9171</v>
+        <v>-0.6513</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.9171</v>
+        <v>-0.6513</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.9171</v>
+        <v>-0.6513</v>
       </c>
       <c r="N65" t="n">
         <v>107</v>
@@ -3436,231 +3436,231 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>FL4MUS</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.9926</v>
+        <v>-0.7252</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.606</v>
+        <v>-0.4427</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8224</v>
+        <v>-0.7328</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.9926</v>
+        <v>-0.7252</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.9926</v>
+        <v>-0.7252</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.9926</v>
+        <v>-0.7252</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9926</v>
+        <v>-0.7252</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.9926</v>
+        <v>-0.7252</v>
       </c>
       <c r="N66" t="n">
-        <v>121</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.0047</v>
+        <v>-0.7691</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.4695</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8272</v>
+        <v>-0.7503</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.0047</v>
+        <v>-0.7691</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.0047</v>
+        <v>-0.7691</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.0047</v>
+        <v>-0.7691</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0047</v>
+        <v>-0.7691</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-1.0047</v>
+        <v>-0.7691</v>
       </c>
       <c r="N67" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0206</v>
+        <v>-0.9926</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.6231</v>
+        <v>-0.606</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8337</v>
+        <v>-0.8394</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.0206</v>
+        <v>-0.9926</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.0206</v>
+        <v>-0.9926</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.0206</v>
+        <v>-0.9926</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.0206</v>
+        <v>-0.9926</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.0206</v>
+        <v>-0.9926</v>
       </c>
       <c r="N68" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1695</v>
+        <v>-1.0047</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.714</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8938</v>
+        <v>-0.8442</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.1695</v>
+        <v>-1.0047</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.1695</v>
+        <v>-1.0047</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.1695</v>
+        <v>-1.0047</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1695</v>
+        <v>-1.0047</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.1695</v>
+        <v>-1.0047</v>
       </c>
       <c r="N69" t="n">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FL4MUS</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.1892</v>
+        <v>-1.1695</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.726</v>
+        <v>-0.714</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9018</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.1892</v>
+        <v>-1.1695</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.1892</v>
+        <v>-1.1695</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.1892</v>
+        <v>-1.1695</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1892</v>
+        <v>-1.1695</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>184</v>
+        <v>113</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.1892</v>
+        <v>-1.1695</v>
       </c>
       <c r="N70" t="n">
-        <v>184</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71">
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.3392</v>
+        <v>-1.3393</v>
       </c>
       <c r="C71" t="n">
         <v>-0.8176</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9624</v>
+        <v>-0.9775</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.3392</v>
+        <v>-1.3393</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0187</v>
+        <v>0.0186</v>
       </c>
       <c r="G71" t="n">
         <v>-1.3579</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0187</v>
+        <v>0.0186</v>
       </c>
       <c r="I71" t="n">
         <v>0.0189</v>
@@ -3722,7 +3722,7 @@
         <v>-0.9428</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0452</v>
+        <v>-1.0592</v>
       </c>
       <c r="E72" t="n">
         <v>-1.5443</v>
@@ -3768,7 +3768,7 @@
         <v>-0.9797</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0697</v>
+        <v>-1.0833</v>
       </c>
       <c r="E73" t="n">
         <v>-1.6048</v>
@@ -3814,7 +3814,7 @@
         <v>-1.0285</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1019</v>
+        <v>-1.1151</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6847</v>
@@ -3860,7 +3860,7 @@
         <v>-1.1099</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1558</v>
+        <v>-1.1682</v>
       </c>
       <c r="E75" t="n">
         <v>-1.818</v>
@@ -3906,7 +3906,7 @@
         <v>-1.1223</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.164</v>
+        <v>-1.1763</v>
       </c>
       <c r="E76" t="n">
         <v>-1.8383</v>
@@ -3952,7 +3952,7 @@
         <v>-1.2079</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2207</v>
+        <v>-1.2322</v>
       </c>
       <c r="E77" t="n">
         <v>-1.9786</v>
@@ -3998,7 +3998,7 @@
         <v>-1.3886</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3403</v>
+        <v>-1.3501</v>
       </c>
       <c r="E78" t="n">
         <v>-2.2746</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.6124</v>
+        <v>-2.5958</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.5949</v>
+        <v>-1.5847</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4767</v>
+        <v>-1.4781</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.6124</v>
+        <v>-2.5958</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.2353</v>
+        <v>-2.2187</v>
       </c>
       <c r="G79" t="n">
         <v>-0.3771</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.2353</v>
+        <v>-2.2187</v>
       </c>
       <c r="I79" t="n">
         <v>-2.2562</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.6106</v>
+        <v>-3.5955</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.2042</v>
+        <v>-2.195</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.88</v>
+        <v>-1.8764</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.6106</v>
+        <v>-3.5955</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.0313</v>
+        <v>-2.0162</v>
       </c>
       <c r="G80" t="n">
         <v>-1.5793</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.0313</v>
+        <v>-2.0162</v>
       </c>
       <c r="I80" t="n">
         <v>-2.0503</v>
@@ -4136,7 +4136,7 @@
         <v>-2.4216</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0238</v>
+        <v>-2.0242</v>
       </c>
       <c r="E81" t="n">
         <v>-3.9667</v>

--- a/database/event/7902/event_7902_evp_summary.xlsx
+++ b/database/event/7902/event_7902_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.955399999999999</v>
+        <v>9.4276</v>
       </c>
       <c r="C2" t="n">
-        <v>5.4672</v>
+        <v>5.7555</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4525</v>
+        <v>3.5973</v>
       </c>
       <c r="E2" t="n">
-        <v>8.955399999999999</v>
+        <v>9.4276</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5894</v>
+        <v>3.5896</v>
       </c>
       <c r="G2" t="n">
-        <v>5.366</v>
+        <v>5.3661</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1312</v>
+        <v>5.1316</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1312</v>
+        <v>5.1316</v>
       </c>
       <c r="J2" t="n">
-        <v>5.366</v>
+        <v>5.3661</v>
       </c>
       <c r="K2" t="n">
         <v>88</v>
@@ -529,7 +529,7 @@
         <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>10.4972</v>
+        <v>10.4977</v>
       </c>
       <c r="N2" t="n">
         <v>245</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.1699</v>
+        <v>7.3668</v>
       </c>
       <c r="C3" t="n">
-        <v>4.3772</v>
+        <v>4.4974</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6397</v>
+        <v>2.6768</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1699</v>
+        <v>7.3668</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4138</v>
+        <v>3.4037</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7561</v>
+        <v>3.7559</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7469</v>
+        <v>4.7246</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7469</v>
+        <v>4.7246</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7561</v>
+        <v>3.7559</v>
       </c>
       <c r="K3" t="n">
         <v>177</v>
@@ -575,7 +575,7 @@
         <v>136</v>
       </c>
       <c r="M3" t="n">
-        <v>8.503</v>
+        <v>8.480499999999999</v>
       </c>
       <c r="N3" t="n">
         <v>313</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7262</v>
+        <v>6.254</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4958</v>
+        <v>3.818</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9825</v>
+        <v>2.1797</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7262</v>
+        <v>6.254</v>
       </c>
       <c r="F4" t="n">
         <v>3.766</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6766</v>
+        <v>5.8118</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4655</v>
+        <v>3.5481</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9599</v>
+        <v>1.9822</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6766</v>
+        <v>5.8118</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2431</v>
+        <v>2.2436</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4335</v>
+        <v>3.4417</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2431</v>
+        <v>2.2436</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2431</v>
+        <v>2.2436</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4335</v>
+        <v>3.4417</v>
       </c>
       <c r="K5" t="n">
         <v>177</v>
@@ -667,7 +667,7 @@
         <v>136</v>
       </c>
       <c r="M5" t="n">
-        <v>5.676600000000001</v>
+        <v>5.6853</v>
       </c>
       <c r="N5" t="n">
         <v>313</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3043</v>
+        <v>5.5843</v>
       </c>
       <c r="C6" t="n">
-        <v>3.2382</v>
+        <v>3.4092</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7904</v>
+        <v>1.8806</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3043</v>
+        <v>5.5843</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2345</v>
+        <v>3.2391</v>
       </c>
       <c r="G6" t="n">
         <v>2.0699</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3543</v>
+        <v>4.3644</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5816</v>
+        <v>4.5922</v>
       </c>
       <c r="J6" t="n">
         <v>2.0699</v>
@@ -713,7 +713,7 @@
         <v>148</v>
       </c>
       <c r="M6" t="n">
-        <v>6.6515</v>
+        <v>6.662100000000001</v>
       </c>
       <c r="N6" t="n">
         <v>404</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.2572</v>
+        <v>5.4153</v>
       </c>
       <c r="C7" t="n">
-        <v>3.2095</v>
+        <v>3.306</v>
       </c>
       <c r="D7" t="n">
-        <v>1.769</v>
+        <v>1.8051</v>
       </c>
       <c r="E7" t="n">
-        <v>5.2572</v>
+        <v>5.4153</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3948</v>
+        <v>3.4004</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8624</v>
+        <v>1.8351</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7052</v>
+        <v>4.7175</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9508</v>
+        <v>4.9638</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8624</v>
+        <v>1.8351</v>
       </c>
       <c r="K7" t="n">
         <v>211</v>
@@ -759,7 +759,7 @@
         <v>104</v>
       </c>
       <c r="M7" t="n">
-        <v>6.8132</v>
+        <v>6.7989</v>
       </c>
       <c r="N7" t="n">
         <v>315</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.0768</v>
+        <v>5.1041</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0994</v>
+        <v>3.116</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6869</v>
+        <v>1.6661</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0768</v>
+        <v>5.1041</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9921</v>
+        <v>3.0396</v>
       </c>
       <c r="G8" t="n">
-        <v>4.0847</v>
+        <v>1.9602</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9921</v>
+        <v>3.9277</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9921</v>
+        <v>3.9277</v>
       </c>
       <c r="J8" t="n">
-        <v>4.0847</v>
+        <v>1.9602</v>
       </c>
       <c r="K8" t="n">
         <v>88</v>
@@ -805,7 +805,7 @@
         <v>157</v>
       </c>
       <c r="M8" t="n">
-        <v>5.0768</v>
+        <v>5.8879</v>
       </c>
       <c r="N8" t="n">
         <v>245</v>
@@ -814,35 +814,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.0029</v>
+        <v>5.0935</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0542</v>
+        <v>3.1095</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6532</v>
+        <v>1.6613</v>
       </c>
       <c r="E9" t="n">
-        <v>5.0029</v>
+        <v>5.0935</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0395</v>
+        <v>0.9925</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9634</v>
+        <v>4.0847</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9275</v>
+        <v>0.9925</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9275</v>
+        <v>0.9925</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9634</v>
+        <v>4.0847</v>
       </c>
       <c r="K9" t="n">
         <v>88</v>
@@ -851,7 +851,7 @@
         <v>157</v>
       </c>
       <c r="M9" t="n">
-        <v>5.8909</v>
+        <v>5.077199999999999</v>
       </c>
       <c r="N9" t="n">
         <v>245</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.9029</v>
+        <v>4.9892</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9932</v>
+        <v>3.0459</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6077</v>
+        <v>1.6147</v>
       </c>
       <c r="E10" t="n">
-        <v>4.9029</v>
+        <v>4.9892</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8744</v>
+        <v>2.882</v>
       </c>
       <c r="G10" t="n">
         <v>2.0285</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5662</v>
+        <v>3.5829</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7524</v>
+        <v>3.7699</v>
       </c>
       <c r="J10" t="n">
         <v>2.0285</v>
@@ -897,7 +897,7 @@
         <v>148</v>
       </c>
       <c r="M10" t="n">
-        <v>5.780900000000001</v>
+        <v>5.7984</v>
       </c>
       <c r="N10" t="n">
         <v>404</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.5641</v>
+        <v>4.5311</v>
       </c>
       <c r="C11" t="n">
-        <v>2.7864</v>
+        <v>2.7662</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4535</v>
+        <v>1.4101</v>
       </c>
       <c r="E11" t="n">
-        <v>4.5641</v>
+        <v>4.5311</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5961</v>
+        <v>1.5963</v>
       </c>
       <c r="G11" t="n">
-        <v>2.968</v>
+        <v>2.9655</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5961</v>
+        <v>1.5963</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5961</v>
+        <v>1.5963</v>
       </c>
       <c r="J11" t="n">
-        <v>2.968</v>
+        <v>2.9655</v>
       </c>
       <c r="K11" t="n">
         <v>88</v>
@@ -943,7 +943,7 @@
         <v>157</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5641</v>
+        <v>4.5618</v>
       </c>
       <c r="N11" t="n">
         <v>245</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.8821</v>
+        <v>4.2174</v>
       </c>
       <c r="C12" t="n">
-        <v>2.37</v>
+        <v>2.5747</v>
       </c>
       <c r="D12" t="n">
-        <v>1.143</v>
+        <v>1.27</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8821</v>
+        <v>4.2174</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8821</v>
+        <v>3.8738</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7717</v>
+        <v>5.7535</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7717</v>
+        <v>5.7535</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.7717</v>
+        <v>5.7535</v>
       </c>
       <c r="N12" t="n">
         <v>174</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.8246</v>
+        <v>3.9482</v>
       </c>
       <c r="C13" t="n">
-        <v>2.3349</v>
+        <v>2.4104</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1168</v>
+        <v>1.1498</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8246</v>
+        <v>3.9482</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5048</v>
+        <v>2.4962</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3198</v>
+        <v>1.3187</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7573</v>
+        <v>2.7385</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7573</v>
+        <v>2.7385</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3198</v>
+        <v>1.3187</v>
       </c>
       <c r="K13" t="n">
         <v>78</v>
@@ -1035,7 +1035,7 @@
         <v>68</v>
       </c>
       <c r="M13" t="n">
-        <v>4.0771</v>
+        <v>4.0572</v>
       </c>
       <c r="N13" t="n">
         <v>146</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2177</v>
+        <v>3.43</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9644</v>
+        <v>2.094</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8406</v>
+        <v>0.9183</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2177</v>
+        <v>3.43</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3746</v>
+        <v>3.374</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1569</v>
+        <v>-0.1572</v>
       </c>
       <c r="H14" t="n">
-        <v>4.661</v>
+        <v>4.6598</v>
       </c>
       <c r="I14" t="n">
-        <v>4.661</v>
+        <v>4.6598</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1569</v>
+        <v>-0.1572</v>
       </c>
       <c r="K14" t="n">
         <v>103</v>
@@ -1081,7 +1081,7 @@
         <v>46</v>
       </c>
       <c r="M14" t="n">
-        <v>4.504099999999999</v>
+        <v>4.502599999999999</v>
       </c>
       <c r="N14" t="n">
         <v>149</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.1094</v>
+        <v>3.2618</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8983</v>
+        <v>1.9913</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7913</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1094</v>
+        <v>3.2618</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1094</v>
+        <v>2.4128</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0805</v>
+        <v>2.5559</v>
       </c>
       <c r="I15" t="n">
-        <v>4.0805</v>
+        <v>2.5559</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
       <c r="K15" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M15" t="n">
-        <v>4.0805</v>
+        <v>3.2156</v>
       </c>
       <c r="N15" t="n">
-        <v>174</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0721</v>
+        <v>3.2256</v>
       </c>
       <c r="C16" t="n">
-        <v>1.8755</v>
+        <v>1.9692</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7743</v>
+        <v>0.827</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0721</v>
+        <v>3.2256</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4124</v>
+        <v>3.1095</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.555</v>
+        <v>4.0808</v>
       </c>
       <c r="I16" t="n">
-        <v>2.555</v>
+        <v>4.0808</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2147</v>
+        <v>4.0808</v>
       </c>
       <c r="N16" t="n">
-        <v>216</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8605</v>
+        <v>3.0504</v>
       </c>
       <c r="C17" t="n">
-        <v>1.7463</v>
+        <v>1.8623</v>
       </c>
       <c r="D17" t="n">
-        <v>0.678</v>
+        <v>0.7487</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8605</v>
+        <v>3.0504</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8605</v>
+        <v>2.8595</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5359</v>
+        <v>3.5337</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5359</v>
+        <v>3.5337</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5359</v>
+        <v>3.5337</v>
       </c>
       <c r="N17" t="n">
         <v>206</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.7794</v>
+        <v>2.9119</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6968</v>
+        <v>1.7777</v>
       </c>
       <c r="D18" t="n">
-        <v>0.641</v>
+        <v>0.6869</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7794</v>
+        <v>2.9119</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6633</v>
+        <v>2.6634</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1161</v>
+        <v>0.1551</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1041</v>
+        <v>3.1044</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1041</v>
+        <v>3.1044</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1161</v>
+        <v>0.1551</v>
       </c>
       <c r="K18" t="n">
         <v>78</v>
@@ -1265,7 +1265,7 @@
         <v>68</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2202</v>
+        <v>3.2595</v>
       </c>
       <c r="N18" t="n">
         <v>146</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.6802</v>
+        <v>2.7458</v>
       </c>
       <c r="C19" t="n">
-        <v>1.6362</v>
+        <v>1.6763</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5959</v>
+        <v>0.6127</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6802</v>
+        <v>2.7458</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3251</v>
+        <v>2.3189</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3551</v>
+        <v>0.3454</v>
       </c>
       <c r="H19" t="n">
-        <v>2.364</v>
+        <v>2.3504</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4874</v>
+        <v>2.4731</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3551</v>
+        <v>0.3454</v>
       </c>
       <c r="K19" t="n">
         <v>211</v>
@@ -1311,7 +1311,7 @@
         <v>104</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8425</v>
+        <v>2.8185</v>
       </c>
       <c r="N19" t="n">
         <v>315</v>
@@ -1320,231 +1320,231 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.6367</v>
+        <v>2.6577</v>
       </c>
       <c r="C20" t="n">
-        <v>1.6097</v>
+        <v>1.6225</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5733</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6367</v>
+        <v>2.6577</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1627</v>
+        <v>2.3224</v>
       </c>
       <c r="G20" t="n">
-        <v>1.474</v>
+        <v>0.2378</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1627</v>
+        <v>2.3581</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2234</v>
+        <v>2.3581</v>
       </c>
       <c r="J20" t="n">
-        <v>1.474</v>
+        <v>0.2378</v>
       </c>
       <c r="K20" t="n">
-        <v>256</v>
+        <v>103</v>
       </c>
       <c r="L20" t="n">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="M20" t="n">
-        <v>2.6974</v>
+        <v>2.5959</v>
       </c>
       <c r="N20" t="n">
-        <v>404</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5402</v>
+        <v>2.5971</v>
       </c>
       <c r="C21" t="n">
-        <v>1.5508</v>
+        <v>1.5855</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5321</v>
+        <v>0.5462</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5402</v>
+        <v>2.5971</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3114</v>
+        <v>1.1699</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2288</v>
+        <v>1.474</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3341</v>
+        <v>1.1699</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3341</v>
+        <v>1.231</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2288</v>
+        <v>1.474</v>
       </c>
       <c r="K21" t="n">
-        <v>103</v>
+        <v>256</v>
       </c>
       <c r="L21" t="n">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="M21" t="n">
-        <v>2.5629</v>
+        <v>2.705</v>
       </c>
       <c r="N21" t="n">
-        <v>149</v>
+        <v>404</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.4456</v>
+        <v>2.4766</v>
       </c>
       <c r="C22" t="n">
-        <v>1.493</v>
+        <v>1.5119</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4891</v>
+        <v>0.4924</v>
       </c>
       <c r="E22" t="n">
-        <v>2.4456</v>
+        <v>2.4766</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4485</v>
+        <v>2.4294</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0029</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.634</v>
+        <v>2.5923</v>
       </c>
       <c r="I22" t="n">
-        <v>2.7715</v>
+        <v>2.5923</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0029</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="L22" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7686</v>
+        <v>2.5923</v>
       </c>
       <c r="N22" t="n">
-        <v>315</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.4294</v>
+        <v>2.4666</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4831</v>
+        <v>1.5058</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4817</v>
+        <v>0.488</v>
       </c>
       <c r="E23" t="n">
-        <v>2.4294</v>
+        <v>2.4666</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4294</v>
+        <v>2.2997</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.0154</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5923</v>
+        <v>2.3085</v>
       </c>
       <c r="I23" t="n">
-        <v>2.5923</v>
+        <v>2.3085</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.0154</v>
       </c>
       <c r="K23" t="n">
-        <v>174</v>
+        <v>103</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M23" t="n">
-        <v>2.5923</v>
+        <v>2.2931</v>
       </c>
       <c r="N23" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.2847</v>
+        <v>2.4504</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3948</v>
+        <v>1.496</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4158</v>
+        <v>0.4807</v>
       </c>
       <c r="E24" t="n">
-        <v>2.2847</v>
+        <v>2.4504</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2999</v>
+        <v>2.4712</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0152</v>
+        <v>-0.0167</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3089</v>
+        <v>2.6838</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3089</v>
+        <v>2.8239</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0152</v>
+        <v>-0.0167</v>
       </c>
       <c r="K24" t="n">
-        <v>103</v>
+        <v>211</v>
       </c>
       <c r="L24" t="n">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="M24" t="n">
-        <v>2.2937</v>
+        <v>2.8072</v>
       </c>
       <c r="N24" t="n">
-        <v>149</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.2613</v>
+        <v>2.3289</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3805</v>
+        <v>1.4218</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4052</v>
+        <v>0.4264</v>
       </c>
       <c r="E25" t="n">
-        <v>2.2613</v>
+        <v>2.3289</v>
       </c>
       <c r="F25" t="n">
-        <v>2.2641</v>
+        <v>2.2654</v>
       </c>
       <c r="G25" t="n">
         <v>-0.0028</v>
       </c>
       <c r="H25" t="n">
-        <v>2.2641</v>
+        <v>2.2654</v>
       </c>
       <c r="I25" t="n">
-        <v>2.2641</v>
+        <v>2.2654</v>
       </c>
       <c r="J25" t="n">
         <v>-0.0028</v>
@@ -1587,7 +1587,7 @@
         <v>46</v>
       </c>
       <c r="M25" t="n">
-        <v>2.2613</v>
+        <v>2.2626</v>
       </c>
       <c r="N25" t="n">
         <v>216</v>
@@ -1596,139 +1596,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.2393</v>
+        <v>2.248</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3671</v>
+        <v>1.3724</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3952</v>
+        <v>0.3903</v>
       </c>
       <c r="E26" t="n">
-        <v>2.2393</v>
+        <v>2.248</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2393</v>
+        <v>2.2125</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2393</v>
+        <v>2.2125</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2393</v>
+        <v>2.2125</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.2393</v>
+        <v>2.2125</v>
       </c>
       <c r="N26" t="n">
-        <v>206</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2135</v>
+        <v>2.2128</v>
       </c>
       <c r="C27" t="n">
-        <v>1.3513</v>
+        <v>1.3509</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3834</v>
+        <v>0.3746</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2135</v>
+        <v>2.2128</v>
       </c>
       <c r="F27" t="n">
-        <v>2.2135</v>
+        <v>2.259</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.2135</v>
+        <v>2.259</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2135</v>
+        <v>2.259</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.2135</v>
+        <v>2.259</v>
       </c>
       <c r="N27" t="n">
-        <v>184</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.1576</v>
+        <v>2.2108</v>
       </c>
       <c r="C28" t="n">
-        <v>1.3172</v>
+        <v>1.3497</v>
       </c>
       <c r="D28" t="n">
-        <v>0.358</v>
+        <v>0.3737</v>
       </c>
       <c r="E28" t="n">
-        <v>2.1576</v>
+        <v>2.2108</v>
       </c>
       <c r="F28" t="n">
-        <v>2.1566</v>
+        <v>2.0555</v>
       </c>
       <c r="G28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.1566</v>
+        <v>2.0555</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1566</v>
+        <v>2.0555</v>
       </c>
       <c r="J28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>76</v>
+        <v>206</v>
       </c>
       <c r="L28" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.1576</v>
+        <v>2.0555</v>
       </c>
       <c r="N28" t="n">
-        <v>167</v>
+        <v>206</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.0854</v>
+        <v>2.205</v>
       </c>
       <c r="C29" t="n">
-        <v>1.2731</v>
+        <v>1.3461</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3251</v>
+        <v>0.3711</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0854</v>
+        <v>2.205</v>
       </c>
       <c r="F29" t="n">
-        <v>2.4511</v>
+        <v>2.4461</v>
       </c>
       <c r="G29" t="n">
         <v>-0.3657</v>
       </c>
       <c r="H29" t="n">
-        <v>2.6397</v>
+        <v>2.6289</v>
       </c>
       <c r="I29" t="n">
-        <v>2.6397</v>
+        <v>2.6289</v>
       </c>
       <c r="J29" t="n">
         <v>-0.3657</v>
@@ -1771,7 +1771,7 @@
         <v>46</v>
       </c>
       <c r="M29" t="n">
-        <v>2.274</v>
+        <v>2.2632</v>
       </c>
       <c r="N29" t="n">
         <v>216</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.0438</v>
+        <v>2.0656</v>
       </c>
       <c r="C30" t="n">
-        <v>1.2477</v>
+        <v>1.261</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3062</v>
+        <v>0.3088</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0438</v>
+        <v>2.0656</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2196</v>
+        <v>2.2201</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1758</v>
+        <v>-0.176</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2196</v>
+        <v>2.2201</v>
       </c>
       <c r="I30" t="n">
-        <v>2.2196</v>
+        <v>2.2201</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1758</v>
+        <v>-0.176</v>
       </c>
       <c r="K30" t="n">
         <v>78</v>
@@ -1817,7 +1817,7 @@
         <v>68</v>
       </c>
       <c r="M30" t="n">
-        <v>2.0438</v>
+        <v>2.0441</v>
       </c>
       <c r="N30" t="n">
         <v>146</v>
@@ -1826,185 +1826,185 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.9528</v>
+        <v>2.0619</v>
       </c>
       <c r="C31" t="n">
-        <v>1.1922</v>
+        <v>1.2588</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2648</v>
+        <v>0.3072</v>
       </c>
       <c r="E31" t="n">
-        <v>1.9528</v>
+        <v>2.0619</v>
       </c>
       <c r="F31" t="n">
-        <v>1.7299</v>
+        <v>2.4982</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2229</v>
+        <v>-0.6068</v>
       </c>
       <c r="H31" t="n">
-        <v>1.7299</v>
+        <v>2.7428</v>
       </c>
       <c r="I31" t="n">
-        <v>1.7299</v>
+        <v>2.7428</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2229</v>
+        <v>-0.6068</v>
       </c>
       <c r="K31" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L31" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="M31" t="n">
-        <v>1.9528</v>
+        <v>2.136</v>
       </c>
       <c r="N31" t="n">
-        <v>146</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.9387</v>
+        <v>2.0595</v>
       </c>
       <c r="C32" t="n">
-        <v>1.1836</v>
+        <v>1.2573</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2583</v>
+        <v>0.3061</v>
       </c>
       <c r="E32" t="n">
-        <v>1.9387</v>
+        <v>2.0595</v>
       </c>
       <c r="F32" t="n">
-        <v>1.9387</v>
+        <v>2.1566</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>1.9387</v>
+        <v>2.1566</v>
       </c>
       <c r="I32" t="n">
-        <v>1.9387</v>
+        <v>2.1566</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="K32" t="n">
-        <v>206</v>
+        <v>76</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M32" t="n">
-        <v>1.9387</v>
+        <v>2.1576</v>
       </c>
       <c r="N32" t="n">
-        <v>206</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.8914</v>
+        <v>1.8817</v>
       </c>
       <c r="C33" t="n">
-        <v>1.1547</v>
+        <v>1.1488</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2368</v>
+        <v>0.2267</v>
       </c>
       <c r="E33" t="n">
-        <v>1.8914</v>
+        <v>1.8817</v>
       </c>
       <c r="F33" t="n">
-        <v>2.4982</v>
+        <v>1.7301</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.6068</v>
+        <v>0.2218</v>
       </c>
       <c r="H33" t="n">
-        <v>2.7428</v>
+        <v>1.7301</v>
       </c>
       <c r="I33" t="n">
-        <v>2.7428</v>
+        <v>1.7301</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6068</v>
+        <v>0.2218</v>
       </c>
       <c r="K33" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L33" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="M33" t="n">
-        <v>2.136</v>
+        <v>1.9519</v>
       </c>
       <c r="N33" t="n">
-        <v>167</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.6274</v>
+        <v>1.7734</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9935</v>
+        <v>1.0826</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1166</v>
+        <v>0.1783</v>
       </c>
       <c r="E34" t="n">
-        <v>1.6274</v>
+        <v>1.7734</v>
       </c>
       <c r="F34" t="n">
-        <v>1.6274</v>
+        <v>1.5548</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.6274</v>
+        <v>1.5548</v>
       </c>
       <c r="I34" t="n">
-        <v>1.6274</v>
+        <v>1.5548</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.6274</v>
+        <v>1.5548</v>
       </c>
       <c r="N34" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.6185</v>
+        <v>1.5363</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9881</v>
+        <v>0.9379</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1126</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>1.6185</v>
+        <v>1.5363</v>
       </c>
       <c r="F35" t="n">
-        <v>1.6185</v>
+        <v>1.6186</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.6185</v>
+        <v>1.6186</v>
       </c>
       <c r="I35" t="n">
-        <v>1.6185</v>
+        <v>1.6186</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.6185</v>
+        <v>1.6186</v>
       </c>
       <c r="N35" t="n">
         <v>121</v>
@@ -2056,139 +2056,139 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.5805</v>
+        <v>1.5227</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9649</v>
+        <v>0.9296</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0953</v>
+        <v>0.0663</v>
       </c>
       <c r="E36" t="n">
-        <v>1.5805</v>
+        <v>1.5227</v>
       </c>
       <c r="F36" t="n">
-        <v>1.5805</v>
+        <v>1.2518</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.5805</v>
+        <v>1.2518</v>
       </c>
       <c r="I36" t="n">
-        <v>1.5805</v>
+        <v>1.2518</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.5805</v>
+        <v>1.2518</v>
       </c>
       <c r="N36" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.4149</v>
+        <v>1.4741</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8638</v>
+        <v>0.8999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0199</v>
+        <v>0.0446</v>
       </c>
       <c r="E37" t="n">
-        <v>1.4149</v>
+        <v>1.4741</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4149</v>
+        <v>1.3745</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4149</v>
+        <v>1.3745</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4149</v>
+        <v>1.3745</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4149</v>
+        <v>1.3745</v>
       </c>
       <c r="N37" t="n">
-        <v>206</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3745</v>
+        <v>1.4583</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8391</v>
+        <v>0.8903</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0015</v>
+        <v>0.0376</v>
       </c>
       <c r="E38" t="n">
-        <v>1.3745</v>
+        <v>1.4583</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3745</v>
+        <v>1.6276</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.3745</v>
+        <v>1.6276</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3745</v>
+        <v>1.6276</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3745</v>
+        <v>1.6276</v>
       </c>
       <c r="N38" t="n">
-        <v>113</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39">
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.3571</v>
+        <v>1.4429</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8285</v>
+        <v>0.8809</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0064</v>
+        <v>0.0307</v>
       </c>
       <c r="E39" t="n">
-        <v>1.3571</v>
+        <v>1.4429</v>
       </c>
       <c r="F39" t="n">
-        <v>1.061</v>
+        <v>1.0604</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2961</v>
+        <v>0.2959</v>
       </c>
       <c r="H39" t="n">
-        <v>1.061</v>
+        <v>1.0604</v>
       </c>
       <c r="I39" t="n">
-        <v>1.061</v>
+        <v>1.0604</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2961</v>
+        <v>0.2959</v>
       </c>
       <c r="K39" t="n">
         <v>103</v>
@@ -2231,7 +2231,7 @@
         <v>46</v>
       </c>
       <c r="M39" t="n">
-        <v>1.3571</v>
+        <v>1.3563</v>
       </c>
       <c r="N39" t="n">
         <v>149</v>
@@ -2240,81 +2240,81 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.352</v>
+        <v>1.4015</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8254</v>
+        <v>0.8556</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.0122</v>
       </c>
       <c r="E40" t="n">
-        <v>1.352</v>
+        <v>1.4015</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4864</v>
+        <v>1.414</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8656</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4864</v>
+        <v>1.414</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4864</v>
+        <v>1.414</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8656</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>88</v>
+        <v>206</v>
       </c>
       <c r="L40" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.352</v>
+        <v>1.414</v>
       </c>
       <c r="N40" t="n">
-        <v>245</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.3324</v>
+        <v>1.263</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8134</v>
+        <v>0.7711</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0177</v>
+        <v>-0.0497</v>
       </c>
       <c r="E41" t="n">
-        <v>1.3324</v>
+        <v>1.263</v>
       </c>
       <c r="F41" t="n">
-        <v>0.396</v>
+        <v>1.8419</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9364</v>
+        <v>-0.6306</v>
       </c>
       <c r="H41" t="n">
-        <v>0.396</v>
+        <v>1.8419</v>
       </c>
       <c r="I41" t="n">
-        <v>0.396</v>
+        <v>1.8419</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9364</v>
+        <v>-0.6306</v>
       </c>
       <c r="K41" t="n">
         <v>177</v>
@@ -2323,7 +2323,7 @@
         <v>136</v>
       </c>
       <c r="M41" t="n">
-        <v>1.3324</v>
+        <v>1.2113</v>
       </c>
       <c r="N41" t="n">
         <v>313</v>
@@ -2332,308 +2332,308 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.2515</v>
+        <v>1.2223</v>
       </c>
       <c r="C42" t="n">
-        <v>0.764</v>
+        <v>0.7462</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0545</v>
+        <v>-0.0678</v>
       </c>
       <c r="E42" t="n">
-        <v>1.2515</v>
+        <v>1.2223</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2515</v>
+        <v>1.1031</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.2515</v>
+        <v>1.1031</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2515</v>
+        <v>1.1031</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.2515</v>
+        <v>1.1031</v>
       </c>
       <c r="N42" t="n">
-        <v>107</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.2111</v>
+        <v>1.1958</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>1.2111</v>
+        <v>1.1958</v>
       </c>
       <c r="F43" t="n">
-        <v>1.8415</v>
+        <v>0.4729</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.6304</v>
+        <v>0.8655</v>
       </c>
       <c r="H43" t="n">
-        <v>1.8415</v>
+        <v>0.4729</v>
       </c>
       <c r="I43" t="n">
-        <v>1.8415</v>
+        <v>0.4729</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.6304</v>
+        <v>0.8655</v>
       </c>
       <c r="K43" t="n">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="L43" t="n">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="M43" t="n">
-        <v>1.2111</v>
+        <v>1.3384</v>
       </c>
       <c r="N43" t="n">
-        <v>313</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.1489</v>
+        <v>1.1856</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7014</v>
+        <v>0.7238</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1012</v>
+        <v>-0.0842</v>
       </c>
       <c r="E44" t="n">
-        <v>1.1489</v>
+        <v>1.1856</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9952</v>
+        <v>0.3963</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1537</v>
+        <v>0.9354</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9952</v>
+        <v>0.3963</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9952</v>
+        <v>0.3963</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1537</v>
+        <v>0.9354</v>
       </c>
       <c r="K44" t="n">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="L44" t="n">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="M44" t="n">
-        <v>1.1489</v>
+        <v>1.3317</v>
       </c>
       <c r="N44" t="n">
-        <v>146</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.1035</v>
+        <v>1.1809</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6737</v>
+        <v>0.7209</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1219</v>
+        <v>-0.0863</v>
       </c>
       <c r="E45" t="n">
-        <v>1.1035</v>
+        <v>1.1809</v>
       </c>
       <c r="F45" t="n">
-        <v>1.1035</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.1534</v>
       </c>
       <c r="H45" t="n">
-        <v>1.1035</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>1.1035</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.1534</v>
       </c>
       <c r="K45" t="n">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M45" t="n">
-        <v>1.1035</v>
+        <v>1.1489</v>
       </c>
       <c r="N45" t="n">
-        <v>184</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>riskyb0b</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9609</v>
+        <v>1.0903</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5866</v>
+        <v>0.6656</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1868</v>
+        <v>-0.1268</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9609</v>
+        <v>1.0903</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3753</v>
+        <v>0.9288</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5856</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3753</v>
+        <v>0.9288</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3753</v>
+        <v>0.9288</v>
       </c>
       <c r="J46" t="n">
-        <v>0.5856</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="L46" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.9609000000000001</v>
+        <v>0.9288</v>
       </c>
       <c r="N46" t="n">
-        <v>167</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9443</v>
+        <v>1.034</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5765</v>
+        <v>0.6313</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1943</v>
+        <v>-0.152</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9443</v>
+        <v>1.034</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.7985</v>
+        <v>0.8883</v>
       </c>
       <c r="G47" t="n">
-        <v>1.7428</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.7985</v>
+        <v>0.8883</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.7985</v>
+        <v>0.8883</v>
       </c>
       <c r="J47" t="n">
-        <v>1.7428</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="L47" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.9442999999999999</v>
+        <v>0.8883</v>
       </c>
       <c r="N47" t="n">
-        <v>313</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>riskyb0b</t>
+          <t>Xant3r</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9258</v>
+        <v>0.8558</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5652</v>
+        <v>0.5225</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2028</v>
+        <v>-0.2316</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9258</v>
+        <v>0.8558</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9258</v>
+        <v>0.8782</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9258</v>
+        <v>0.8782</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9258</v>
+        <v>0.8782</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.9258</v>
+        <v>0.8782</v>
       </c>
       <c r="N48" t="n">
         <v>101</v>
@@ -2654,216 +2654,216 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8111</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5554</v>
+        <v>0.4952</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.21</v>
+        <v>-0.2515</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8111</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3199</v>
+        <v>0.3753</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5899</v>
+        <v>0.5856</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3199</v>
+        <v>0.3753</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3199</v>
+        <v>0.3753</v>
       </c>
       <c r="J49" t="n">
-        <v>0.5899</v>
+        <v>0.5856</v>
       </c>
       <c r="K49" t="n">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="L49" t="n">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="M49" t="n">
-        <v>0.9097999999999999</v>
+        <v>0.9609000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>216</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8894</v>
+        <v>0.7914</v>
       </c>
       <c r="C50" t="n">
-        <v>0.543</v>
+        <v>0.4831</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2193</v>
+        <v>-0.2603</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8894</v>
+        <v>0.7914</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8894</v>
+        <v>0.6873</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8894</v>
+        <v>0.6873</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8894</v>
+        <v>0.6873</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8894</v>
+        <v>0.6873</v>
       </c>
       <c r="N50" t="n">
-        <v>174</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8894</v>
+        <v>0.7808</v>
       </c>
       <c r="C51" t="n">
-        <v>0.543</v>
+        <v>0.4767</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2193</v>
+        <v>-0.2651</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8894</v>
+        <v>0.7808</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8894</v>
+        <v>-0.7982</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1.7426</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8894</v>
+        <v>-0.7982</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8894</v>
+        <v>-0.7982</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1.7426</v>
       </c>
       <c r="K51" t="n">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M51" t="n">
-        <v>0.8894</v>
+        <v>0.9443999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>117</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Xant3r</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8648</v>
+        <v>0.7724</v>
       </c>
       <c r="C52" t="n">
-        <v>0.528</v>
+        <v>0.4715</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2305</v>
+        <v>-0.2688</v>
       </c>
       <c r="E52" t="n">
-        <v>0.8648</v>
+        <v>0.7724</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8648</v>
+        <v>0.9011</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8648</v>
+        <v>0.9011</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8648</v>
+        <v>0.9011</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.8648</v>
+        <v>0.9011</v>
       </c>
       <c r="N52" t="n">
-        <v>101</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6868</v>
+        <v>0.7333</v>
       </c>
       <c r="C53" t="n">
-        <v>0.4193</v>
+        <v>0.4477</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3116</v>
+        <v>-0.2863</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6868</v>
+        <v>0.7333</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6868</v>
+        <v>0.5538</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6868</v>
+        <v>0.5538</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6868</v>
+        <v>0.5538</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.6868</v>
+        <v>0.5538</v>
       </c>
       <c r="N53" t="n">
         <v>107</v>
@@ -2884,185 +2884,185 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6026</v>
+        <v>0.7286</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3679</v>
+        <v>0.4448</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3499</v>
+        <v>-0.2884</v>
       </c>
       <c r="E54" t="n">
-        <v>0.6026</v>
+        <v>0.7286</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6026</v>
+        <v>0.5986</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6026</v>
+        <v>0.5986</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6026</v>
+        <v>0.5986</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6026</v>
+        <v>0.5986</v>
       </c>
       <c r="N54" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5881</v>
+        <v>0.6902</v>
       </c>
       <c r="C55" t="n">
-        <v>0.359</v>
+        <v>0.4214</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3565</v>
+        <v>-0.3055</v>
       </c>
       <c r="E55" t="n">
-        <v>0.5881</v>
+        <v>0.6902</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5881</v>
+        <v>0.2963</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.5899</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5881</v>
+        <v>0.2963</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5881</v>
+        <v>0.2963</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>0.5899</v>
       </c>
       <c r="K55" t="n">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M55" t="n">
-        <v>0.5881</v>
+        <v>0.8862</v>
       </c>
       <c r="N55" t="n">
-        <v>117</v>
+        <v>216</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5536</v>
+        <v>0.4046</v>
       </c>
       <c r="C56" t="n">
-        <v>0.338</v>
+        <v>0.247</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.3722</v>
+        <v>-0.4331</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5536</v>
+        <v>0.4046</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5536</v>
+        <v>0.1809</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5536</v>
+        <v>0.1809</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5536</v>
+        <v>0.1809</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5536</v>
+        <v>0.1809</v>
       </c>
       <c r="N56" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.3878</v>
       </c>
       <c r="C57" t="n">
-        <v>0.3179</v>
+        <v>0.2367</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.3872</v>
+        <v>-0.4406</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.3878</v>
       </c>
       <c r="F57" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4555</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4555</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4555</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4555</v>
       </c>
       <c r="N57" t="n">
-        <v>206</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58">
@@ -3072,31 +3072,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5081</v>
+        <v>0.3402</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3102</v>
+        <v>0.2077</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.3929</v>
+        <v>-0.4619</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5081</v>
+        <v>0.3402</v>
       </c>
       <c r="F58" t="n">
-        <v>1.1599</v>
+        <v>1.1594</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.6518</v>
+        <v>-0.672</v>
       </c>
       <c r="H58" t="n">
-        <v>1.1599</v>
+        <v>1.1594</v>
       </c>
       <c r="I58" t="n">
-        <v>1.2204</v>
+        <v>1.2199</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.6518</v>
+        <v>-0.672</v>
       </c>
       <c r="K58" t="n">
         <v>211</v>
@@ -3105,7 +3105,7 @@
         <v>104</v>
       </c>
       <c r="M58" t="n">
-        <v>0.5685999999999999</v>
+        <v>0.5478999999999999</v>
       </c>
       <c r="N58" t="n">
         <v>315</v>
@@ -3114,32 +3114,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4555</v>
+        <v>0.3294</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2781</v>
+        <v>0.2011</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4169</v>
+        <v>-0.4667</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4555</v>
+        <v>0.3294</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4555</v>
+        <v>0.6026</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.4555</v>
+        <v>0.6026</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4555</v>
+        <v>0.6026</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.4555</v>
+        <v>0.6026</v>
       </c>
       <c r="N59" t="n">
         <v>113</v>
@@ -3160,124 +3160,124 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>khaN</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3724</v>
+        <v>0.2503</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2273</v>
+        <v>0.1528</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.4547</v>
+        <v>-0.502</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3724</v>
+        <v>0.2503</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3724</v>
+        <v>0.3473</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3724</v>
+        <v>0.3473</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3724</v>
+        <v>0.3473</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.3724</v>
+        <v>0.3473</v>
       </c>
       <c r="N60" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>khaN</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.3481</v>
+        <v>0.2088</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2125</v>
+        <v>0.1275</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.4657</v>
+        <v>-0.5206</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3481</v>
+        <v>0.2088</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3481</v>
+        <v>0.5198</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3481</v>
+        <v>0.5198</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3481</v>
+        <v>0.5198</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.3481</v>
+        <v>0.5198</v>
       </c>
       <c r="N61" t="n">
-        <v>101</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.1808</v>
+        <v>0.1539</v>
       </c>
       <c r="C62" t="n">
-        <v>0.1104</v>
+        <v>0.094</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5419</v>
+        <v>-0.5451</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1808</v>
+        <v>0.1539</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1808</v>
+        <v>0.1719</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1808</v>
+        <v>0.1719</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1808</v>
+        <v>0.1719</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1808</v>
+        <v>0.1719</v>
       </c>
       <c r="N62" t="n">
         <v>121</v>
@@ -3298,32 +3298,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.1719</v>
+        <v>0.0196</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1049</v>
+        <v>0.012</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.546</v>
+        <v>-0.6051</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1719</v>
+        <v>0.0196</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1719</v>
+        <v>0.3725</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1719</v>
+        <v>0.3725</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1719</v>
+        <v>0.3725</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1719</v>
+        <v>0.3725</v>
       </c>
       <c r="N63" t="n">
         <v>121</v>
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.2508</v>
+        <v>-0.2687</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1531</v>
+        <v>-0.164</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.7338</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.2508</v>
+        <v>-0.2687</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6263</v>
       </c>
       <c r="G64" t="n">
         <v>-0.8783</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6263</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6603</v>
+        <v>0.659</v>
       </c>
       <c r="J64" t="n">
         <v>-0.8783</v>
@@ -3381,7 +3381,7 @@
         <v>148</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.218</v>
+        <v>-0.2192999999999999</v>
       </c>
       <c r="N64" t="n">
         <v>404</v>
@@ -3390,277 +3390,277 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.2603</v>
+        <v>-0.2702</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1589</v>
+        <v>-0.165</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7427</v>
+        <v>-0.7345</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.2603</v>
+        <v>-0.2702</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.2603</v>
+        <v>-0.2767</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.2603</v>
+        <v>-0.2767</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2603</v>
+        <v>-0.2767</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.2603</v>
+        <v>-0.2767</v>
       </c>
       <c r="N65" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>FL4MUS</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.2766</v>
+        <v>-0.2779</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1689</v>
+        <v>-0.1697</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7501</v>
+        <v>-0.738</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.2766</v>
+        <v>-0.2779</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2766</v>
+        <v>-0.2495</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.2766</v>
+        <v>-0.2495</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2766</v>
+        <v>-0.2495</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>117</v>
+        <v>184</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.2766</v>
+        <v>-0.2495</v>
       </c>
       <c r="N66" t="n">
-        <v>117</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FL4MUS</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.2855</v>
+        <v>-0.3883</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1743</v>
+        <v>-0.2371</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7542</v>
+        <v>-0.7873</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.2855</v>
+        <v>-0.3883</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.2855</v>
+        <v>-0.2603</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.2855</v>
+        <v>-0.2603</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2855</v>
+        <v>-0.2603</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>184</v>
+        <v>113</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.2855</v>
+        <v>-0.2603</v>
       </c>
       <c r="N67" t="n">
-        <v>184</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C4LLM3SU3</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.3336</v>
+        <v>-0.442</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2037</v>
+        <v>-0.2698</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7761</v>
+        <v>-0.8113</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.3336</v>
+        <v>-0.442</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.3336</v>
+        <v>-0.4714</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.3336</v>
+        <v>-0.4714</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3336</v>
+        <v>-0.4714</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.3336</v>
+        <v>-0.4714</v>
       </c>
       <c r="N68" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4607</v>
+        <v>-0.5511</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2813</v>
+        <v>-0.3364</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8339</v>
+        <v>-0.86</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4607</v>
+        <v>-0.5511</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4607</v>
+        <v>-0.5921</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4607</v>
+        <v>-0.5921</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4607</v>
+        <v>-0.5921</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.4607</v>
+        <v>-0.5921</v>
       </c>
       <c r="N69" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>C4LLM3SU3</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.5918</v>
+        <v>-0.5776</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3613</v>
+        <v>-0.3526</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.8718</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.5918</v>
+        <v>-0.5776</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.5918</v>
+        <v>-0.3333</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.5918</v>
+        <v>-0.3333</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5918</v>
+        <v>-0.3333</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.5918</v>
+        <v>-0.3333</v>
       </c>
       <c r="N70" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="71">
@@ -3670,16 +3670,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.754</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4603</v>
+        <v>-0.4883</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9674</v>
+        <v>-0.9711</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.754</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="F71" t="n">
         <v>-0.754</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.7916</v>
+        <v>-0.9271</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4833</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9846</v>
+        <v>-1.0279</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.7916</v>
+        <v>-0.9271</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.7916</v>
+        <v>-0.7922</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.7916</v>
+        <v>-0.7922</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.7916</v>
+        <v>-0.7922</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.7916</v>
+        <v>-0.7922</v>
       </c>
       <c r="N72" t="n">
         <v>184</v>
@@ -3758,139 +3758,139 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1eeR</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.0019</v>
+        <v>-1.3216</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6117</v>
+        <v>-0.8068</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0803</v>
+        <v>-1.2042</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0019</v>
+        <v>-1.3216</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.0019</v>
+        <v>-0.468</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>-0.6567</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.0019</v>
+        <v>-0.468</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.0019</v>
+        <v>-0.468</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>-0.6567</v>
       </c>
       <c r="K73" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.0019</v>
+        <v>-1.1247</v>
       </c>
       <c r="N73" t="n">
-        <v>101</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>1eeR</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.1247</v>
+        <v>-1.3379</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6866</v>
+        <v>-0.8168</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1362</v>
+        <v>-1.2114</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1247</v>
+        <v>-1.3379</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.468</v>
+        <v>-1.0105</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.6567</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.468</v>
+        <v>-1.0105</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.468</v>
+        <v>-1.0105</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.6567</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="L74" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.1247</v>
+        <v>-1.0105</v>
       </c>
       <c r="N74" t="n">
-        <v>167</v>
+        <v>101</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.2587</v>
+        <v>-1.6191</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7684</v>
+        <v>-0.9885</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1972</v>
+        <v>-1.337</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.2587</v>
+        <v>-1.6191</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.2587</v>
+        <v>-1.3896</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.2587</v>
+        <v>-1.3896</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2587</v>
+        <v>-1.3896</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>117</v>
+        <v>184</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.2587</v>
+        <v>-1.3896</v>
       </c>
       <c r="N75" t="n">
-        <v>117</v>
+        <v>184</v>
       </c>
     </row>
     <row r="76">
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.3073</v>
+        <v>-1.7209</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7981</v>
+        <v>-1.0506</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2193</v>
+        <v>-1.3825</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.3073</v>
+        <v>-1.7209</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.3073</v>
+        <v>-1.3363</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.3073</v>
+        <v>-1.3363</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.3073</v>
+        <v>-1.3363</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.3073</v>
+        <v>-1.3363</v>
       </c>
       <c r="N76" t="n">
         <v>107</v>
@@ -3942,139 +3942,139 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.3889</v>
+        <v>-1.7503</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.8479</v>
+        <v>-1.0685</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2565</v>
+        <v>-1.3956</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.3889</v>
+        <v>-1.7503</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.3889</v>
+        <v>-1.2799</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>-0.2937</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.3889</v>
+        <v>-1.2799</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.3889</v>
+        <v>-1.3467</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>-0.2937</v>
       </c>
       <c r="K77" t="n">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.3889</v>
+        <v>-1.6404</v>
       </c>
       <c r="N77" t="n">
-        <v>184</v>
+        <v>404</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.566</v>
+        <v>-1.8866</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.956</v>
+        <v>-1.1518</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3371</v>
+        <v>-1.4565</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.566</v>
+        <v>-1.8866</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.0985</v>
+        <v>-1.2588</v>
       </c>
       <c r="G78" t="n">
-        <v>0.5325</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.0985</v>
+        <v>-1.2588</v>
       </c>
       <c r="I78" t="n">
-        <v>-2.0985</v>
+        <v>-1.2588</v>
       </c>
       <c r="J78" t="n">
-        <v>0.5325</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="L78" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.566</v>
+        <v>-1.2588</v>
       </c>
       <c r="N78" t="n">
-        <v>149</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.6044</v>
+        <v>-1.9158</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.9795</v>
+        <v>-1.1696</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3546</v>
+        <v>-1.4696</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.6044</v>
+        <v>-1.9158</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.3107</v>
+        <v>-2.0989</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.2937</v>
+        <v>0.5319</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.3107</v>
+        <v>-2.0989</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.3791</v>
+        <v>-2.0989</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.2937</v>
+        <v>0.5319</v>
       </c>
       <c r="K79" t="n">
-        <v>256</v>
+        <v>103</v>
       </c>
       <c r="L79" t="n">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.6728</v>
+        <v>-1.567</v>
       </c>
       <c r="N79" t="n">
-        <v>404</v>
+        <v>149</v>
       </c>
     </row>
     <row r="80">
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.8697</v>
+        <v>-3.0677</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.7519</v>
+        <v>-1.8728</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.9305</v>
+        <v>-1.9841</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.8697</v>
+        <v>-3.0677</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.4424</v>
+        <v>-1.443</v>
       </c>
       <c r="G80" t="n">
-        <v>-1.4273</v>
+        <v>-1.4757</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.4424</v>
+        <v>-1.443</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.5177</v>
+        <v>-1.5183</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.4273</v>
+        <v>-1.4757</v>
       </c>
       <c r="K80" t="n">
         <v>211</v>
@@ -4117,7 +4117,7 @@
         <v>104</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.945</v>
+        <v>-2.994</v>
       </c>
       <c r="N80" t="n">
         <v>315</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.214</v>
+        <v>-3.5767</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.9621</v>
+        <v>-2.1836</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0873</v>
+        <v>-2.2115</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.214</v>
+        <v>-3.5767</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.8419</v>
+        <v>-2.8702</v>
       </c>
       <c r="G81" t="n">
         <v>-0.3721</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.8419</v>
+        <v>-2.8702</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.8419</v>
+        <v>-2.8702</v>
       </c>
       <c r="J81" t="n">
         <v>-0.3721</v>
@@ -4163,7 +4163,7 @@
         <v>46</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.214</v>
+        <v>-3.2423</v>
       </c>
       <c r="N81" t="n">
         <v>216</v>
@@ -4269,10 +4269,10 @@
         <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2353</v>
+        <v>0.2347</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2354</v>
+        <v>4.2246</v>
       </c>
     </row>
     <row r="3">
@@ -4306,13 +4306,13 @@
         <v>18</v>
       </c>
       <c r="H3" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1656</v>
+        <v>-0.1549</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.9808</v>
+        <v>-2.7882</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1867</v>
+        <v>-0.1869</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.3606</v>
+        <v>-3.3642</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.339</v>
+        <v>-0.3392</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.102</v>
+        <v>-6.1056</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.429</v>
+        <v>-0.4292</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.722</v>
+        <v>-7.7256</v>
       </c>
     </row>
     <row r="7">
@@ -4669,10 +4669,10 @@
         <v>1.97</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7692</v>
+        <v>1.7696</v>
       </c>
       <c r="J12" t="n">
-        <v>30.0764</v>
+        <v>30.0832</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5637</v>
+        <v>1.564</v>
       </c>
       <c r="J13" t="n">
-        <v>26.5829</v>
+        <v>26.588</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.47</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0299</v>
+        <v>1.0302</v>
       </c>
       <c r="J14" t="n">
-        <v>17.5083</v>
+        <v>17.5134</v>
       </c>
     </row>
     <row r="15">
@@ -4786,13 +4786,13 @@
         <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5654</v>
+        <v>0.5441</v>
       </c>
       <c r="J15" t="n">
-        <v>9.611800000000001</v>
+        <v>9.249700000000001</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>1.14</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3612</v>
+        <v>0.3615</v>
       </c>
       <c r="J16" t="n">
-        <v>6.1404</v>
+        <v>6.1455</v>
       </c>
     </row>
     <row r="17">
@@ -5269,10 +5269,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7662</v>
+        <v>0.7652</v>
       </c>
       <c r="J27" t="n">
-        <v>14.5578</v>
+        <v>14.5388</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>0.92</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1117</v>
+        <v>-0.1119</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.1223</v>
+        <v>-2.1261</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>0.83</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2085</v>
+        <v>-0.2087</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.9615</v>
+        <v>-3.9653</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.74</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2955</v>
+        <v>-0.2957</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.6145</v>
+        <v>-5.6183</v>
       </c>
     </row>
     <row r="31">
@@ -5426,13 +5426,13 @@
         <v>19</v>
       </c>
       <c r="H31" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.612</v>
+        <v>-0.6038</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.628</v>
+        <v>-11.4722</v>
       </c>
     </row>
     <row r="32">
@@ -7269,10 +7269,10 @@
         <v>1.77</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2811</v>
+        <v>1.2815</v>
       </c>
       <c r="J77" t="n">
-        <v>24.3409</v>
+        <v>24.3485</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.36</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7429</v>
+        <v>0.7431</v>
       </c>
       <c r="J78" t="n">
-        <v>14.1151</v>
+        <v>14.1189</v>
       </c>
     </row>
     <row r="79">
@@ -7346,13 +7346,13 @@
         <v>19</v>
       </c>
       <c r="H79" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7151</v>
+        <v>0.7013</v>
       </c>
       <c r="J79" t="n">
-        <v>13.5869</v>
+        <v>13.3247</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>1.24</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5687</v>
+        <v>0.5689</v>
       </c>
       <c r="J80" t="n">
-        <v>10.8053</v>
+        <v>10.8091</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.93</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3183</v>
+        <v>-0.318</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.0477</v>
+        <v>-6.042</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.51</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7867</v>
+        <v>0.7861</v>
       </c>
       <c r="J82" t="n">
-        <v>17.3074</v>
+        <v>17.2942</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2108</v>
+        <v>0.2105</v>
       </c>
       <c r="J83" t="n">
-        <v>4.6376</v>
+        <v>4.631</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>1.02</v>
       </c>
       <c r="I84" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0722</v>
       </c>
       <c r="J84" t="n">
-        <v>1.5928</v>
+        <v>1.5884</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.75</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3018</v>
+        <v>-0.302</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.6396</v>
+        <v>-6.644</v>
       </c>
     </row>
     <row r="86">
@@ -7626,13 +7626,13 @@
         <v>22</v>
       </c>
       <c r="H86" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3577</v>
+        <v>-0.3487</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.8694</v>
+        <v>-7.6714</v>
       </c>
     </row>
     <row r="87">
@@ -8469,10 +8469,10 @@
         <v>1.4</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8312</v>
+        <v>0.8308</v>
       </c>
       <c r="J107" t="n">
-        <v>18.2864</v>
+        <v>18.2776</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.34</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7429</v>
+        <v>0.7425</v>
       </c>
       <c r="J108" t="n">
-        <v>16.3438</v>
+        <v>16.335</v>
       </c>
     </row>
     <row r="109">
@@ -8546,13 +8546,13 @@
         <v>22</v>
       </c>
       <c r="H109" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4383</v>
+        <v>0.4571</v>
       </c>
       <c r="J109" t="n">
-        <v>9.6426</v>
+        <v>10.0562</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.99</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0808</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.7776</v>
+        <v>-1.7864</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6812</v>
+        <v>-0.6815</v>
       </c>
       <c r="J111" t="n">
-        <v>-14.9864</v>
+        <v>-14.993</v>
       </c>
     </row>
     <row r="112">
@@ -9469,10 +9469,10 @@
         <v>1.15</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3624</v>
+        <v>0.3613</v>
       </c>
       <c r="J132" t="n">
-        <v>7.6104</v>
+        <v>7.5873</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.14</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3439</v>
+        <v>0.3428</v>
       </c>
       <c r="J133" t="n">
-        <v>7.2219</v>
+        <v>7.1988</v>
       </c>
     </row>
     <row r="134">
@@ -9546,13 +9546,13 @@
         <v>21</v>
       </c>
       <c r="H134" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2466</v>
+        <v>0.2856</v>
       </c>
       <c r="J134" t="n">
-        <v>5.1786</v>
+        <v>5.9976</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.9</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1413</v>
+        <v>-0.1416</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.9673</v>
+        <v>-2.9736</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.38</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.618</v>
+        <v>-0.6182</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.978</v>
+        <v>-12.9822</v>
       </c>
     </row>
     <row r="137">
@@ -9666,13 +9666,13 @@
         <v>21</v>
       </c>
       <c r="H137" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I137" t="n">
-        <v>1.2104</v>
+        <v>1.2007</v>
       </c>
       <c r="J137" t="n">
-        <v>25.4184</v>
+        <v>25.2147</v>
       </c>
     </row>
     <row r="138">
@@ -9706,13 +9706,13 @@
         <v>21</v>
       </c>
       <c r="H138" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6256</v>
+        <v>0.6118</v>
       </c>
       <c r="J138" t="n">
-        <v>13.1376</v>
+        <v>12.8478</v>
       </c>
     </row>
     <row r="139">
@@ -9746,13 +9746,13 @@
         <v>21</v>
       </c>
       <c r="H139" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4311</v>
+        <v>0.4109</v>
       </c>
       <c r="J139" t="n">
-        <v>9.053100000000001</v>
+        <v>8.6289</v>
       </c>
     </row>
     <row r="140">
@@ -9786,13 +9786,13 @@
         <v>21</v>
       </c>
       <c r="H140" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2057</v>
+        <v>-0.266</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.3197</v>
+        <v>-5.586</v>
       </c>
     </row>
     <row r="141">
@@ -9826,13 +9826,13 @@
         <v>21</v>
       </c>
       <c r="H141" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2681</v>
+        <v>-0.2954</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.6301</v>
+        <v>-6.2034</v>
       </c>
     </row>
     <row r="142">
@@ -11469,10 +11469,10 @@
         <v>1.43</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8135</v>
+        <v>0.8127</v>
       </c>
       <c r="J182" t="n">
-        <v>17.0835</v>
+        <v>17.0667</v>
       </c>
     </row>
     <row r="183">
@@ -11506,13 +11506,13 @@
         <v>21</v>
       </c>
       <c r="H183" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I183" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.1069</v>
       </c>
       <c r="J183" t="n">
-        <v>1.6842</v>
+        <v>2.2449</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>0.96</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0698</v>
+        <v>-0.0699</v>
       </c>
       <c r="J184" t="n">
-        <v>-1.4658</v>
+        <v>-1.4679</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>0.8</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.248</v>
+        <v>-0.2481</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.208</v>
+        <v>-5.2101</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.55</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4766</v>
+        <v>-0.4768</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.0086</v>
+        <v>-10.0128</v>
       </c>
     </row>
     <row r="187">
@@ -12269,10 +12269,10 @@
         <v>1.57</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9653</v>
+        <v>0.9647</v>
       </c>
       <c r="J202" t="n">
-        <v>23.1672</v>
+        <v>23.1528</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.37</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6821</v>
+        <v>0.6816</v>
       </c>
       <c r="J203" t="n">
-        <v>16.3704</v>
+        <v>16.3584</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>0.93</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1186</v>
+        <v>-0.1188</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.8464</v>
+        <v>-2.8512</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2499</v>
+        <v>-0.2501</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.9976</v>
+        <v>-6.0024</v>
       </c>
     </row>
     <row r="206">
@@ -12426,13 +12426,13 @@
         <v>24</v>
       </c>
       <c r="H206" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3083</v>
+        <v>-0.299</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.3992</v>
+        <v>-7.176</v>
       </c>
     </row>
     <row r="207">
@@ -12466,13 +12466,13 @@
         <v>24</v>
       </c>
       <c r="H207" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1782</v>
+        <v>1.165</v>
       </c>
       <c r="J207" t="n">
-        <v>28.2768</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>1.38</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9172</v>
+        <v>0.9177</v>
       </c>
       <c r="J208" t="n">
-        <v>22.0128</v>
+        <v>22.0248</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>1.24</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6333</v>
+        <v>0.6337</v>
       </c>
       <c r="J209" t="n">
-        <v>15.1992</v>
+        <v>15.2088</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.98</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1306</v>
+        <v>-0.1302</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.1344</v>
+        <v>-3.1248</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.73</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.777</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="J211" t="n">
-        <v>-18.648</v>
+        <v>-18.6408</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.36</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8832</v>
+        <v>0.8837</v>
       </c>
       <c r="J212" t="n">
-        <v>16.7808</v>
+        <v>16.7903</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.18</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5063</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J213" t="n">
-        <v>9.6197</v>
+        <v>9.625400000000001</v>
       </c>
     </row>
     <row r="214">
@@ -12746,13 +12746,13 @@
         <v>19</v>
       </c>
       <c r="H214" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4615</v>
+        <v>0.4392</v>
       </c>
       <c r="J214" t="n">
-        <v>8.7685</v>
+        <v>8.344799999999999</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>1.1</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3172</v>
+        <v>0.3175</v>
       </c>
       <c r="J215" t="n">
-        <v>6.0268</v>
+        <v>6.0325</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.98</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.127</v>
+        <v>-0.1266</v>
       </c>
       <c r="J216" t="n">
-        <v>-2.413</v>
+        <v>-2.4054</v>
       </c>
     </row>
     <row r="217">
@@ -13269,10 +13269,10 @@
         <v>1.24</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4944</v>
+        <v>0.4939</v>
       </c>
       <c r="J227" t="n">
-        <v>26.2032</v>
+        <v>26.1767</v>
       </c>
     </row>
     <row r="228">
@@ -13306,13 +13306,13 @@
         <v>53</v>
       </c>
       <c r="H228" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2481</v>
+        <v>0.267</v>
       </c>
       <c r="J228" t="n">
-        <v>13.1493</v>
+        <v>14.151</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.06</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1665</v>
+        <v>0.1663</v>
       </c>
       <c r="J229" t="n">
-        <v>8.8245</v>
+        <v>8.8139</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.89</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1605</v>
+        <v>-0.1607</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.506500000000001</v>
+        <v>-8.517099999999999</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.84</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2142</v>
+        <v>-0.2144</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.3526</v>
+        <v>-11.3632</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.93</v>
       </c>
       <c r="I232" t="n">
-        <v>0.988</v>
+        <v>0.9877</v>
       </c>
       <c r="J232" t="n">
-        <v>16.796</v>
+        <v>16.7909</v>
       </c>
     </row>
     <row r="233">
@@ -13549,10 +13549,10 @@
         <v>1.32</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4183</v>
+        <v>0.4182</v>
       </c>
       <c r="J234" t="n">
-        <v>7.1111</v>
+        <v>7.1094</v>
       </c>
     </row>
     <row r="235">
@@ -13586,13 +13586,13 @@
         <v>17</v>
       </c>
       <c r="H235" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3289</v>
+        <v>0.3403</v>
       </c>
       <c r="J235" t="n">
-        <v>5.5913</v>
+        <v>5.7851</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>1.23</v>
       </c>
       <c r="I236" t="n">
-        <v>0.3172</v>
+        <v>0.3171</v>
       </c>
       <c r="J236" t="n">
-        <v>5.3924</v>
+        <v>5.3907</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>0.78</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.2327</v>
+        <v>-0.2331</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.9559</v>
+        <v>-3.9627</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>0.67</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3388</v>
+        <v>-0.3391</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.7596</v>
+        <v>-5.7647</v>
       </c>
     </row>
     <row r="239">
@@ -13746,13 +13746,13 @@
         <v>17</v>
       </c>
       <c r="H239" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3562</v>
+        <v>-0.3478</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.0554</v>
+        <v>-5.9126</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>0.61</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3902</v>
+        <v>-0.3904</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.6334</v>
+        <v>-6.6368</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.52</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4692</v>
+        <v>-0.4695</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.9764</v>
+        <v>-7.9815</v>
       </c>
     </row>
     <row r="242">
@@ -14869,10 +14869,10 @@
         <v>1.31</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6019</v>
+        <v>0.5999</v>
       </c>
       <c r="J267" t="n">
-        <v>13.8437</v>
+        <v>13.7977</v>
       </c>
     </row>
     <row r="268">
@@ -14906,13 +14906,13 @@
         <v>23</v>
       </c>
       <c r="H268" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1647</v>
+        <v>0.1849</v>
       </c>
       <c r="J268" t="n">
-        <v>3.7881</v>
+        <v>4.2527</v>
       </c>
     </row>
     <row r="269">
@@ -14946,13 +14946,13 @@
         <v>23</v>
       </c>
       <c r="H269" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0024</v>
+        <v>0.0955</v>
       </c>
       <c r="J269" t="n">
-        <v>-0.0552</v>
+        <v>2.1965</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1024</v>
+        <v>-0.1031</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.3552</v>
+        <v>-2.3713</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.9</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1505</v>
+        <v>-0.1512</v>
       </c>
       <c r="J271" t="n">
-        <v>-3.4615</v>
+        <v>-3.4776</v>
       </c>
     </row>
     <row r="272">
@@ -17066,13 +17066,13 @@
         <v>24</v>
       </c>
       <c r="H322" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5371</v>
+        <v>0.5264</v>
       </c>
       <c r="J322" t="n">
-        <v>12.8904</v>
+        <v>12.6336</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.07</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1379</v>
+        <v>0.138</v>
       </c>
       <c r="J323" t="n">
-        <v>3.3096</v>
+        <v>3.312</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>1.07</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1379</v>
+        <v>0.138</v>
       </c>
       <c r="J324" t="n">
-        <v>3.3096</v>
+        <v>3.312</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.95</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.0895</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J325" t="n">
-        <v>-2.148</v>
+        <v>-2.1456</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.74</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3143</v>
+        <v>-0.3141</v>
       </c>
       <c r="J326" t="n">
-        <v>-7.5432</v>
+        <v>-7.5384</v>
       </c>
     </row>
     <row r="327">
@@ -19038,7 +19038,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -19078,7 +19078,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -19638,7 +19638,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -20158,7 +20158,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -20518,7 +20518,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -20666,13 +20666,13 @@
         <v>21</v>
       </c>
       <c r="H412" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4136</v>
+        <v>1.4258</v>
       </c>
       <c r="J412" t="n">
-        <v>29.6856</v>
+        <v>29.9418</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.29</v>
       </c>
       <c r="I413" t="n">
-        <v>0.7269</v>
+        <v>0.7266</v>
       </c>
       <c r="J413" t="n">
-        <v>15.2649</v>
+        <v>15.2586</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.24</v>
       </c>
       <c r="I414" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6253</v>
       </c>
       <c r="J414" t="n">
-        <v>13.1355</v>
+        <v>13.1313</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>1.1</v>
       </c>
       <c r="I415" t="n">
-        <v>0.3047</v>
+        <v>0.3044</v>
       </c>
       <c r="J415" t="n">
-        <v>6.3987</v>
+        <v>6.3924</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.8</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.6309</v>
+        <v>-0.6313</v>
       </c>
       <c r="J416" t="n">
-        <v>-13.2489</v>
+        <v>-13.2573</v>
       </c>
     </row>
     <row r="417">
@@ -21469,10 +21469,10 @@
         <v>1.27</v>
       </c>
       <c r="I432" t="n">
-        <v>0.7251</v>
+        <v>0.7245</v>
       </c>
       <c r="J432" t="n">
-        <v>29.7291</v>
+        <v>29.7045</v>
       </c>
     </row>
     <row r="433">
@@ -21509,10 +21509,10 @@
         <v>1.2</v>
       </c>
       <c r="I433" t="n">
-        <v>0.5708</v>
+        <v>0.5703</v>
       </c>
       <c r="J433" t="n">
-        <v>23.4028</v>
+        <v>23.3823</v>
       </c>
     </row>
     <row r="434">
@@ -21549,10 +21549,10 @@
         <v>1.06</v>
       </c>
       <c r="I434" t="n">
-        <v>0.2212</v>
+        <v>0.2211</v>
       </c>
       <c r="J434" t="n">
-        <v>9.0692</v>
+        <v>9.065099999999999</v>
       </c>
     </row>
     <row r="435">
@@ -21586,13 +21586,13 @@
         <v>41</v>
       </c>
       <c r="H435" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I435" t="n">
-        <v>-0.1792</v>
+        <v>-0.1459</v>
       </c>
       <c r="J435" t="n">
-        <v>-7.3472</v>
+        <v>-5.9819</v>
       </c>
     </row>
     <row r="436">
@@ -21629,10 +21629,10 @@
         <v>0.8</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.5994</v>
+        <v>-0.5998</v>
       </c>
       <c r="J436" t="n">
-        <v>-24.5754</v>
+        <v>-24.5918</v>
       </c>
     </row>
     <row r="437">
@@ -21669,10 +21669,10 @@
         <v>1.5</v>
       </c>
       <c r="I437" t="n">
-        <v>0.8838</v>
+        <v>0.8825</v>
       </c>
       <c r="J437" t="n">
-        <v>36.2358</v>
+        <v>36.1825</v>
       </c>
     </row>
     <row r="438">
@@ -21706,13 +21706,13 @@
         <v>41</v>
       </c>
       <c r="H438" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I438" t="n">
-        <v>0.2262</v>
+        <v>0.2451</v>
       </c>
       <c r="J438" t="n">
-        <v>9.2742</v>
+        <v>10.0491</v>
       </c>
     </row>
     <row r="439">
@@ -21749,10 +21749,10 @@
         <v>0.95</v>
       </c>
       <c r="I439" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.0897</v>
       </c>
       <c r="J439" t="n">
-        <v>-3.6654</v>
+        <v>-3.6777</v>
       </c>
     </row>
     <row r="440">
@@ -21789,10 +21789,10 @@
         <v>0.88</v>
       </c>
       <c r="I440" t="n">
-        <v>-0.173</v>
+        <v>-0.1733</v>
       </c>
       <c r="J440" t="n">
-        <v>-7.093</v>
+        <v>-7.1053</v>
       </c>
     </row>
     <row r="441">
@@ -21826,13 +21826,13 @@
         <v>41</v>
       </c>
       <c r="H441" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.266</v>
+        <v>-0.2565</v>
       </c>
       <c r="J441" t="n">
-        <v>-10.906</v>
+        <v>-10.5165</v>
       </c>
     </row>
     <row r="442">
@@ -21866,13 +21866,13 @@
         <v>21</v>
       </c>
       <c r="H442" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I442" t="n">
-        <v>0.342</v>
+        <v>0.3552</v>
       </c>
       <c r="J442" t="n">
-        <v>7.182</v>
+        <v>7.4592</v>
       </c>
     </row>
     <row r="443">
@@ -21909,10 +21909,10 @@
         <v>1</v>
       </c>
       <c r="I443" t="n">
-        <v>0.008</v>
+        <v>0.0077</v>
       </c>
       <c r="J443" t="n">
-        <v>0.168</v>
+        <v>0.1617</v>
       </c>
     </row>
     <row r="444">
@@ -21949,10 +21949,10 @@
         <v>0.86</v>
       </c>
       <c r="I444" t="n">
-        <v>-0.1841</v>
+        <v>-0.1843</v>
       </c>
       <c r="J444" t="n">
-        <v>-3.8661</v>
+        <v>-3.8703</v>
       </c>
     </row>
     <row r="445">
@@ -21989,10 +21989,10 @@
         <v>0.82</v>
       </c>
       <c r="I445" t="n">
-        <v>-0.2253</v>
+        <v>-0.2255</v>
       </c>
       <c r="J445" t="n">
-        <v>-4.7313</v>
+        <v>-4.7355</v>
       </c>
     </row>
     <row r="446">
@@ -22029,10 +22029,10 @@
         <v>0.75</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.2938</v>
+        <v>-0.294</v>
       </c>
       <c r="J446" t="n">
-        <v>-6.1698</v>
+        <v>-6.174</v>
       </c>
     </row>
     <row r="447">
@@ -22069,10 +22069,10 @@
         <v>1.46</v>
       </c>
       <c r="I447" t="n">
-        <v>0.5853</v>
+        <v>0.585</v>
       </c>
       <c r="J447" t="n">
-        <v>12.2913</v>
+        <v>12.285</v>
       </c>
     </row>
     <row r="448">
@@ -22109,10 +22109,10 @@
         <v>1.21</v>
       </c>
       <c r="I448" t="n">
-        <v>0.3112</v>
+        <v>0.311</v>
       </c>
       <c r="J448" t="n">
-        <v>6.5352</v>
+        <v>6.531</v>
       </c>
     </row>
     <row r="449">
@@ -22149,10 +22149,10 @@
         <v>1.19</v>
       </c>
       <c r="I449" t="n">
-        <v>0.2878</v>
+        <v>0.2877</v>
       </c>
       <c r="J449" t="n">
-        <v>6.0438</v>
+        <v>6.0417</v>
       </c>
     </row>
     <row r="450">
@@ -22186,13 +22186,13 @@
         <v>21</v>
       </c>
       <c r="H450" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I450" t="n">
-        <v>0.1988</v>
+        <v>0.2121</v>
       </c>
       <c r="J450" t="n">
-        <v>4.1748</v>
+        <v>4.4541</v>
       </c>
     </row>
     <row r="451">
@@ -22229,10 +22229,10 @@
         <v>0.98</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.0573</v>
+        <v>-0.0575</v>
       </c>
       <c r="J451" t="n">
-        <v>-1.2033</v>
+        <v>-1.2075</v>
       </c>
     </row>
     <row r="452">
@@ -22269,10 +22269,10 @@
         <v>1.57</v>
       </c>
       <c r="I452" t="n">
-        <v>1.1908</v>
+        <v>1.1903</v>
       </c>
       <c r="J452" t="n">
-        <v>25.0068</v>
+        <v>24.9963</v>
       </c>
     </row>
     <row r="453">
@@ -22309,10 +22309,10 @@
         <v>1.56</v>
       </c>
       <c r="I453" t="n">
-        <v>1.1774</v>
+        <v>1.177</v>
       </c>
       <c r="J453" t="n">
-        <v>24.7254</v>
+        <v>24.717</v>
       </c>
     </row>
     <row r="454">
@@ -22349,10 +22349,10 @@
         <v>1.53</v>
       </c>
       <c r="I454" t="n">
-        <v>1.1371</v>
+        <v>1.1367</v>
       </c>
       <c r="J454" t="n">
-        <v>23.8791</v>
+        <v>23.8707</v>
       </c>
     </row>
     <row r="455">
@@ -22386,13 +22386,13 @@
         <v>21</v>
       </c>
       <c r="H455" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.1781</v>
+        <v>-0.1418</v>
       </c>
       <c r="J455" t="n">
-        <v>-3.7401</v>
+        <v>-2.9778</v>
       </c>
     </row>
     <row r="456">
@@ -22429,10 +22429,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I456" t="n">
-        <v>-1.1341</v>
+        <v>-1.1343</v>
       </c>
       <c r="J456" t="n">
-        <v>-23.8161</v>
+        <v>-23.8203</v>
       </c>
     </row>
     <row r="457">
@@ -22466,13 +22466,13 @@
         <v>21</v>
       </c>
       <c r="H457" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I457" t="n">
-        <v>0.7875</v>
+        <v>0.7728</v>
       </c>
       <c r="J457" t="n">
-        <v>16.5375</v>
+        <v>16.2288</v>
       </c>
     </row>
     <row r="458">
@@ -22509,10 +22509,10 @@
         <v>1.07</v>
       </c>
       <c r="I458" t="n">
-        <v>0.2112</v>
+        <v>0.2117</v>
       </c>
       <c r="J458" t="n">
-        <v>4.4352</v>
+        <v>4.4457</v>
       </c>
     </row>
     <row r="459">
@@ -22549,10 +22549,10 @@
         <v>1.01</v>
       </c>
       <c r="I459" t="n">
-        <v>0.0586</v>
+        <v>0.059</v>
       </c>
       <c r="J459" t="n">
-        <v>1.2306</v>
+        <v>1.239</v>
       </c>
     </row>
     <row r="460">
@@ -22589,10 +22589,10 @@
         <v>0.54</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.4811</v>
+        <v>-0.4809</v>
       </c>
       <c r="J460" t="n">
-        <v>-10.1031</v>
+        <v>-10.0989</v>
       </c>
     </row>
     <row r="461">
@@ -22629,10 +22629,10 @@
         <v>0.5</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.5154</v>
+        <v>-0.5152</v>
       </c>
       <c r="J461" t="n">
-        <v>-10.8234</v>
+        <v>-10.8192</v>
       </c>
     </row>
     <row r="462">
@@ -22669,10 +22669,10 @@
         <v>1.63</v>
       </c>
       <c r="I462" t="n">
-        <v>1.273</v>
+        <v>1.2725</v>
       </c>
       <c r="J462" t="n">
-        <v>25.46</v>
+        <v>25.45</v>
       </c>
     </row>
     <row r="463">
@@ -22706,13 +22706,13 @@
         <v>20</v>
       </c>
       <c r="H463" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="I463" t="n">
-        <v>0.9953</v>
+        <v>1.0111</v>
       </c>
       <c r="J463" t="n">
-        <v>19.906</v>
+        <v>20.222</v>
       </c>
     </row>
     <row r="464">
@@ -22749,10 +22749,10 @@
         <v>1.26</v>
       </c>
       <c r="I464" t="n">
-        <v>0.6673</v>
+        <v>0.667</v>
       </c>
       <c r="J464" t="n">
-        <v>13.346</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="465">
@@ -22789,10 +22789,10 @@
         <v>1.21</v>
       </c>
       <c r="I465" t="n">
-        <v>0.5642</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J465" t="n">
-        <v>11.284</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="466">
@@ -22829,10 +22829,10 @@
         <v>0.6</v>
       </c>
       <c r="I466" t="n">
-        <v>-1.0536</v>
+        <v>-1.0539</v>
       </c>
       <c r="J466" t="n">
-        <v>-21.072</v>
+        <v>-21.078</v>
       </c>
     </row>
     <row r="467">
@@ -24838,7 +24838,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -26869,10 +26869,10 @@
         <v>1.16</v>
       </c>
       <c r="I567" t="n">
-        <v>0.4321</v>
+        <v>0.4331</v>
       </c>
       <c r="J567" t="n">
-        <v>8.641999999999999</v>
+        <v>8.662000000000001</v>
       </c>
     </row>
     <row r="568">
@@ -26906,13 +26906,13 @@
         <v>20</v>
       </c>
       <c r="H568" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I568" t="n">
-        <v>0.0452</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J568" t="n">
-        <v>0.904</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="569">
@@ -26949,10 +26949,10 @@
         <v>0.77</v>
       </c>
       <c r="I569" t="n">
-        <v>-0.2614</v>
+        <v>-0.2612</v>
       </c>
       <c r="J569" t="n">
-        <v>-5.228</v>
+        <v>-5.224</v>
       </c>
     </row>
     <row r="570">
@@ -26989,10 +26989,10 @@
         <v>0.53</v>
       </c>
       <c r="I570" t="n">
-        <v>-0.4782</v>
+        <v>-0.478</v>
       </c>
       <c r="J570" t="n">
-        <v>-9.564</v>
+        <v>-9.56</v>
       </c>
     </row>
     <row r="571">
@@ -27029,10 +27029,10 @@
         <v>0.48</v>
       </c>
       <c r="I571" t="n">
-        <v>-0.5216</v>
+        <v>-0.5214</v>
       </c>
       <c r="J571" t="n">
-        <v>-10.432</v>
+        <v>-10.428</v>
       </c>
     </row>
     <row r="572">
@@ -27066,13 +27066,13 @@
         <v>19</v>
       </c>
       <c r="H572" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I572" t="n">
-        <v>1.0779</v>
+        <v>1.0644</v>
       </c>
       <c r="J572" t="n">
-        <v>20.4801</v>
+        <v>20.2236</v>
       </c>
     </row>
     <row r="573">
@@ -27109,10 +27109,10 @@
         <v>1.46</v>
       </c>
       <c r="I573" t="n">
-        <v>1.035</v>
+        <v>1.0354</v>
       </c>
       <c r="J573" t="n">
-        <v>19.665</v>
+        <v>19.6726</v>
       </c>
     </row>
     <row r="574">
@@ -27149,10 +27149,10 @@
         <v>1.29</v>
       </c>
       <c r="I574" t="n">
-        <v>0.7228</v>
+        <v>0.723</v>
       </c>
       <c r="J574" t="n">
-        <v>13.7332</v>
+        <v>13.737</v>
       </c>
     </row>
     <row r="575">
@@ -27189,10 +27189,10 @@
         <v>1.25</v>
       </c>
       <c r="I575" t="n">
-        <v>0.6434</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="J575" t="n">
-        <v>12.2246</v>
+        <v>12.2284</v>
       </c>
     </row>
     <row r="576">
@@ -27229,10 +27229,10 @@
         <v>0.83</v>
       </c>
       <c r="I576" t="n">
-        <v>-0.5659</v>
+        <v>-0.5655</v>
       </c>
       <c r="J576" t="n">
-        <v>-10.7521</v>
+        <v>-10.7445</v>
       </c>
     </row>
     <row r="577">
@@ -27269,10 +27269,10 @@
         <v>1.31</v>
       </c>
       <c r="I577" t="n">
-        <v>0.6773</v>
+        <v>0.6763</v>
       </c>
       <c r="J577" t="n">
-        <v>12.8687</v>
+        <v>12.8497</v>
       </c>
     </row>
     <row r="578">
@@ -27309,10 +27309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I578" t="n">
-        <v>-0.2267</v>
+        <v>-0.2269</v>
       </c>
       <c r="J578" t="n">
-        <v>-4.3073</v>
+        <v>-4.3111</v>
       </c>
     </row>
     <row r="579">
@@ -27349,10 +27349,10 @@
         <v>0.79</v>
       </c>
       <c r="I579" t="n">
-        <v>-0.2461</v>
+        <v>-0.2462</v>
       </c>
       <c r="J579" t="n">
-        <v>-4.6759</v>
+        <v>-4.6778</v>
       </c>
     </row>
     <row r="580">
@@ -27386,13 +27386,13 @@
         <v>19</v>
       </c>
       <c r="H580" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="I580" t="n">
-        <v>-0.3765</v>
+        <v>-0.3586</v>
       </c>
       <c r="J580" t="n">
-        <v>-7.1535</v>
+        <v>-6.8134</v>
       </c>
     </row>
     <row r="581">
@@ -27426,13 +27426,13 @@
         <v>19</v>
       </c>
       <c r="H581" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I581" t="n">
-        <v>-0.4301</v>
+        <v>-0.4391</v>
       </c>
       <c r="J581" t="n">
-        <v>-8.171900000000001</v>
+        <v>-8.3429</v>
       </c>
     </row>
     <row r="582">
@@ -27469,10 +27469,10 @@
         <v>1.22</v>
       </c>
       <c r="I582" t="n">
-        <v>0.4838</v>
+        <v>0.4832</v>
       </c>
       <c r="J582" t="n">
-        <v>11.1274</v>
+        <v>11.1136</v>
       </c>
     </row>
     <row r="583">
@@ -27506,13 +27506,13 @@
         <v>23</v>
       </c>
       <c r="H583" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="I583" t="n">
-        <v>0.3418</v>
+        <v>0.3598</v>
       </c>
       <c r="J583" t="n">
-        <v>7.8614</v>
+        <v>8.275399999999999</v>
       </c>
     </row>
     <row r="584">
@@ -27549,10 +27549,10 @@
         <v>0.91</v>
       </c>
       <c r="I584" t="n">
-        <v>-0.1306</v>
+        <v>-0.1307</v>
       </c>
       <c r="J584" t="n">
-        <v>-3.0038</v>
+        <v>-3.0061</v>
       </c>
     </row>
     <row r="585">
@@ -27589,10 +27589,10 @@
         <v>0.8</v>
       </c>
       <c r="I585" t="n">
-        <v>-0.2468</v>
+        <v>-0.247</v>
       </c>
       <c r="J585" t="n">
-        <v>-5.6764</v>
+        <v>-5.681</v>
       </c>
     </row>
     <row r="586">
@@ -27629,10 +27629,10 @@
         <v>0.63</v>
       </c>
       <c r="I586" t="n">
-        <v>-0.4055</v>
+        <v>-0.4057</v>
       </c>
       <c r="J586" t="n">
-        <v>-9.326499999999999</v>
+        <v>-9.331099999999999</v>
       </c>
     </row>
     <row r="587">
@@ -28069,10 +28069,10 @@
         <v>1.24</v>
       </c>
       <c r="I597" t="n">
-        <v>0.6515</v>
+        <v>0.6525</v>
       </c>
       <c r="J597" t="n">
-        <v>19.545</v>
+        <v>19.575</v>
       </c>
     </row>
     <row r="598">
@@ -28106,13 +28106,13 @@
         <v>30</v>
       </c>
       <c r="H598" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I598" t="n">
-        <v>0.3998</v>
+        <v>0.3759</v>
       </c>
       <c r="J598" t="n">
-        <v>11.994</v>
+        <v>11.277</v>
       </c>
     </row>
     <row r="599">
@@ -28149,10 +28149,10 @@
         <v>1.08</v>
       </c>
       <c r="I599" t="n">
-        <v>0.2735</v>
+        <v>0.2739</v>
       </c>
       <c r="J599" t="n">
-        <v>8.205</v>
+        <v>8.217000000000001</v>
       </c>
     </row>
     <row r="600">
@@ -28189,10 +28189,10 @@
         <v>1.06</v>
       </c>
       <c r="I600" t="n">
-        <v>0.2176</v>
+        <v>0.2182</v>
       </c>
       <c r="J600" t="n">
-        <v>6.528</v>
+        <v>6.546</v>
       </c>
     </row>
     <row r="601">
@@ -28226,13 +28226,13 @@
         <v>30</v>
       </c>
       <c r="H601" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I601" t="n">
-        <v>-0.2475</v>
+        <v>-0.2761</v>
       </c>
       <c r="J601" t="n">
-        <v>-7.425</v>
+        <v>-8.282999999999999</v>
       </c>
     </row>
     <row r="602">
@@ -28518,7 +28518,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -29269,10 +29269,10 @@
         <v>1.8</v>
       </c>
       <c r="I627" t="n">
-        <v>1.469</v>
+        <v>1.4695</v>
       </c>
       <c r="J627" t="n">
-        <v>29.38</v>
+        <v>29.39</v>
       </c>
     </row>
     <row r="628">
@@ -29309,10 +29309,10 @@
         <v>1.45</v>
       </c>
       <c r="I628" t="n">
-        <v>1.0112</v>
+        <v>1.0115</v>
       </c>
       <c r="J628" t="n">
-        <v>20.224</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="629">
@@ -29346,13 +29346,13 @@
         <v>20</v>
       </c>
       <c r="H629" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I629" t="n">
-        <v>0.8139</v>
+        <v>0.7951</v>
       </c>
       <c r="J629" t="n">
-        <v>16.278</v>
+        <v>15.902</v>
       </c>
     </row>
     <row r="630">
@@ -29389,10 +29389,10 @@
         <v>1.2</v>
       </c>
       <c r="I630" t="n">
-        <v>0.5305</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J630" t="n">
-        <v>10.61</v>
+        <v>10.614</v>
       </c>
     </row>
     <row r="631">
@@ -29429,10 +29429,10 @@
         <v>0.78</v>
       </c>
       <c r="I631" t="n">
-        <v>-0.6884</v>
+        <v>-0.6881</v>
       </c>
       <c r="J631" t="n">
-        <v>-13.768</v>
+        <v>-13.762</v>
       </c>
     </row>
     <row r="632">
@@ -29669,10 +29669,10 @@
         <v>1.68</v>
       </c>
       <c r="I637" t="n">
-        <v>1.3262</v>
+        <v>1.3267</v>
       </c>
       <c r="J637" t="n">
-        <v>23.8716</v>
+        <v>23.8806</v>
       </c>
     </row>
     <row r="638">
@@ -29709,10 +29709,10 @@
         <v>1.44</v>
       </c>
       <c r="I638" t="n">
-        <v>1.0019</v>
+        <v>1.0022</v>
       </c>
       <c r="J638" t="n">
-        <v>18.0342</v>
+        <v>18.0396</v>
       </c>
     </row>
     <row r="639">
@@ -29749,16 +29749,16 @@
         <v>1.26</v>
       </c>
       <c r="I639" t="n">
-        <v>0.6624</v>
+        <v>0.6626</v>
       </c>
       <c r="J639" t="n">
-        <v>11.9232</v>
+        <v>11.9268</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -29789,10 +29789,10 @@
         <v>1.06</v>
       </c>
       <c r="I640" t="n">
-        <v>0.1869</v>
+        <v>0.1872</v>
       </c>
       <c r="J640" t="n">
-        <v>3.3642</v>
+        <v>3.3696</v>
       </c>
     </row>
     <row r="641">
@@ -29826,13 +29826,13 @@
         <v>18</v>
       </c>
       <c r="H641" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I641" t="n">
-        <v>-0.2807</v>
+        <v>-0.3097</v>
       </c>
       <c r="J641" t="n">
-        <v>-5.0526</v>
+        <v>-5.5746</v>
       </c>
     </row>
     <row r="642">
@@ -29866,13 +29866,13 @@
         <v>20</v>
       </c>
       <c r="H642" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="I642" t="n">
-        <v>1.8037</v>
+        <v>1.7925</v>
       </c>
       <c r="J642" t="n">
-        <v>36.074</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="643">
@@ -29909,10 +29909,10 @@
         <v>1.48</v>
       </c>
       <c r="I643" t="n">
-        <v>1.0532</v>
+        <v>1.0535</v>
       </c>
       <c r="J643" t="n">
-        <v>21.064</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="644">
@@ -29949,10 +29949,10 @@
         <v>1.38</v>
       </c>
       <c r="I644" t="n">
-        <v>0.8873</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="J644" t="n">
-        <v>17.746</v>
+        <v>17.752</v>
       </c>
     </row>
     <row r="645">
@@ -29989,10 +29989,10 @@
         <v>0.97</v>
       </c>
       <c r="I645" t="n">
-        <v>-0.1932</v>
+        <v>-0.1929</v>
       </c>
       <c r="J645" t="n">
-        <v>-3.864</v>
+        <v>-3.858</v>
       </c>
     </row>
     <row r="646">
@@ -30029,10 +30029,10 @@
         <v>0.74</v>
       </c>
       <c r="I646" t="n">
-        <v>-0.7785</v>
+        <v>-0.7782</v>
       </c>
       <c r="J646" t="n">
-        <v>-15.57</v>
+        <v>-15.564</v>
       </c>
     </row>
     <row r="647">
@@ -30869,10 +30869,10 @@
         <v>1.01</v>
       </c>
       <c r="I667" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0795</v>
       </c>
       <c r="J667" t="n">
-        <v>1.4526</v>
+        <v>1.431</v>
       </c>
     </row>
     <row r="668">
@@ -30909,10 +30909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I668" t="n">
-        <v>-0.0825</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J668" t="n">
-        <v>-1.485</v>
+        <v>-1.4958</v>
       </c>
     </row>
     <row r="669">
@@ -30946,13 +30946,13 @@
         <v>18</v>
       </c>
       <c r="H669" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="I669" t="n">
-        <v>-0.12</v>
+        <v>-0.096</v>
       </c>
       <c r="J669" t="n">
-        <v>-2.16</v>
+        <v>-1.728</v>
       </c>
     </row>
     <row r="670">
@@ -30989,10 +30989,10 @@
         <v>0.64</v>
       </c>
       <c r="I670" t="n">
-        <v>-0.3842</v>
+        <v>-0.3846</v>
       </c>
       <c r="J670" t="n">
-        <v>-6.9156</v>
+        <v>-6.9228</v>
       </c>
     </row>
     <row r="671">
@@ -31029,10 +31029,10 @@
         <v>0.59</v>
       </c>
       <c r="I671" t="n">
-        <v>-0.4288</v>
+        <v>-0.4292</v>
       </c>
       <c r="J671" t="n">
-        <v>-7.7184</v>
+        <v>-7.7256</v>
       </c>
     </row>
     <row r="672">
@@ -32469,10 +32469,10 @@
         <v>1.55</v>
       </c>
       <c r="I707" t="n">
-        <v>1.1425</v>
+        <v>1.1428</v>
       </c>
       <c r="J707" t="n">
-        <v>18.28</v>
+        <v>18.2848</v>
       </c>
     </row>
     <row r="708">
@@ -32509,10 +32509,10 @@
         <v>1.47</v>
       </c>
       <c r="I708" t="n">
-        <v>1.0348</v>
+        <v>1.0351</v>
       </c>
       <c r="J708" t="n">
-        <v>16.5568</v>
+        <v>16.5616</v>
       </c>
     </row>
     <row r="709">
@@ -32546,13 +32546,13 @@
         <v>16</v>
       </c>
       <c r="H709" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="I709" t="n">
-        <v>0.9023</v>
+        <v>0.8842</v>
       </c>
       <c r="J709" t="n">
-        <v>14.4368</v>
+        <v>14.1472</v>
       </c>
     </row>
     <row r="710">
@@ -32589,10 +32589,10 @@
         <v>1.29</v>
       </c>
       <c r="I710" t="n">
-        <v>0.7129</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="J710" t="n">
-        <v>11.4064</v>
+        <v>11.4112</v>
       </c>
     </row>
     <row r="711">
@@ -32629,10 +32629,10 @@
         <v>1.09</v>
       </c>
       <c r="I711" t="n">
-        <v>0.2582</v>
+        <v>0.2585</v>
       </c>
       <c r="J711" t="n">
-        <v>4.1312</v>
+        <v>4.136</v>
       </c>
     </row>
   </sheetData>
